--- a/data/UK_OBR_inflation.xlsx
+++ b/data/UK_OBR_inflation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ac0918bc62ee91db/Documents/1 OLLIE/0. R/Macro_und_Revision/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ac0918bc62ee91db/Documents/1 OLLIE/0. R/UK_economic_model/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{B155730B-A8D9-49EC-9749-3718F3665132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84F636D4-053F-463C-AEAF-4A755A9788FE}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{B155730B-A8D9-49EC-9749-3718F3665132}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{512A190E-7C51-40F1-A21D-88ED93204729}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" activeTab="2" xr2:uid="{BCFE34D0-EE09-4408-B65A-C43F7378E982}"/>
   </bookViews>
@@ -17,10 +17,26 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -644,7 +660,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -824,6 +840,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -985,16 +1007,17 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1051,6 +1074,108 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="data"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="56">
+          <cell r="B56">
+            <v>4.0999999999999996</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="B57">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="B58">
+            <v>1.3</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="B59">
+            <v>1.4</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="B60">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="B61">
+            <v>1.7</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="B62">
+            <v>2.1</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="B63">
+            <v>2.4</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="B64">
+            <v>2.7</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="B65">
+            <v>2.9</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="B66">
+            <v>3.1</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="B67">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="B68">
+            <v>3.3</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="B69">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="B70">
+            <v>1.3</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="B71">
+            <v>2.5</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="B72">
+            <v>1.5</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5557,7 +5682,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{507CC110-C502-47F8-A414-94DFAC14B0EE}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{507CC110-C502-47F8-A414-94DFAC14B0EE}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="B3:R142" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisCol" showAll="0">
@@ -16139,24 +16264,10 @@
       <c r="B5" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="F5">
         <v>68.099999999999994</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3">
+      <c r="R5">
         <v>68.099999999999994</v>
       </c>
     </row>
@@ -16164,26 +16275,13 @@
       <c r="B6" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3">
+      <c r="F6">
         <v>68.900000000000006</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3">
+      <c r="N6">
         <v>216.7</v>
       </c>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3">
+      <c r="R6">
         <v>285.60000000000002</v>
       </c>
     </row>
@@ -16191,26 +16289,13 @@
       <c r="B7" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3">
+      <c r="F7">
         <v>68.900000000000006</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3">
+      <c r="N7">
         <v>227.63</v>
       </c>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3">
+      <c r="R7">
         <v>296.52999999999997</v>
       </c>
     </row>
@@ -16218,26 +16303,13 @@
       <c r="B8" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3">
+      <c r="F8">
         <v>69.400000000000006</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3">
+      <c r="N8">
         <v>229.86</v>
       </c>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3">
+      <c r="R8">
         <v>299.26</v>
       </c>
     </row>
@@ -16245,30 +16317,19 @@
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3">
+      <c r="E9">
         <v>1.908957416</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9">
         <v>69.400000000000006</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3">
+      <c r="N9">
         <v>241.65</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3">
+      <c r="Q9">
         <v>2.8647568290000001</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9">
         <v>315.82371424500002</v>
       </c>
     </row>
@@ -16276,32 +16337,22 @@
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3">
+      <c r="E10">
         <v>1.5965166909999999</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10">
         <v>70</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3">
+      <c r="M10">
         <v>4.2316566680000003</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10">
         <v>225.87</v>
       </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3">
+      <c r="Q10">
         <v>2.5590551179999999</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10">
         <v>304.25722847700001</v>
       </c>
     </row>
@@ -16309,32 +16360,22 @@
       <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3">
+      <c r="E11">
         <v>2.0319303340000001</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11">
         <v>70.3</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3">
+      <c r="M11">
         <v>0.38659227699999998</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11">
         <v>228.51</v>
       </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3">
+      <c r="Q11">
         <v>2.8141361260000002</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11">
         <v>304.04265873700001</v>
       </c>
     </row>
@@ -16342,32 +16383,22 @@
       <c r="B12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3">
+      <c r="E12">
         <v>1.729106628</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12">
         <v>70.599999999999994</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3">
+      <c r="M12">
         <v>2.3579570169999999</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12">
         <v>235.28</v>
       </c>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3">
+      <c r="Q12">
         <v>2.7958387519999999</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12">
         <v>312.762902397</v>
       </c>
     </row>
@@ -16375,32 +16406,22 @@
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3">
+      <c r="E13">
         <v>1.585014409</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13">
         <v>70.5</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3">
+      <c r="M13">
         <v>-0.87316366599999995</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13">
         <v>239.54</v>
       </c>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3">
+      <c r="Q13">
         <v>2.5906735749999998</v>
       </c>
-      <c r="R13" s="3">
+      <c r="R13">
         <v>313.34252431799996</v>
       </c>
     </row>
@@ -16408,32 +16429,22 @@
       <c r="B14" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3">
+      <c r="E14">
         <v>1.8571428569999999</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14">
         <v>71.3</v>
       </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3">
+      <c r="M14">
         <v>14.769557710000001</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14">
         <v>259.23</v>
       </c>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3">
+      <c r="Q14">
         <v>2.9430582209999998</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14">
         <v>350.09975878800003</v>
       </c>
     </row>
@@ -16441,32 +16452,22 @@
       <c r="B15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3">
+      <c r="E15">
         <v>1.280227596</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15">
         <v>71.2</v>
       </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3">
+      <c r="M15">
         <v>19.911601243</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15">
         <v>274.01</v>
       </c>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3">
+      <c r="Q15">
         <v>2.5461489500000001</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R15">
         <v>368.94797778899999</v>
       </c>
     </row>
@@ -16474,32 +16475,22 @@
       <c r="B16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3">
+      <c r="E16">
         <v>1.416430595</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16">
         <v>71.599999999999994</v>
       </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3">
+      <c r="M16">
         <v>25.055253315000002</v>
       </c>
-      <c r="N16" s="3">
+      <c r="N16">
         <v>294.23</v>
       </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3">
+      <c r="Q16">
         <v>2.5300442759999999</v>
       </c>
-      <c r="R16" s="3">
+      <c r="R16">
         <v>394.83172818600002</v>
       </c>
     </row>
@@ -16507,32 +16498,22 @@
       <c r="B17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3">
+      <c r="E17">
         <v>1.5602836879999999</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17">
         <v>71.599999999999994</v>
       </c>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3">
+      <c r="M17">
         <v>29.853051682</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17">
         <v>311.05</v>
       </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3">
+      <c r="Q17">
         <v>2.525252525</v>
       </c>
-      <c r="R17" s="3">
+      <c r="R17">
         <v>416.58858789499999</v>
       </c>
     </row>
@@ -16540,32 +16521,22 @@
       <c r="B18" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3">
+      <c r="E18">
         <v>1.402524544</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18">
         <v>72.3</v>
       </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3">
+      <c r="M18">
         <v>20.113412798999999</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18">
         <v>311.37</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3">
+      <c r="Q18">
         <v>2.2995649469999999</v>
       </c>
-      <c r="R18" s="3">
+      <c r="R18">
         <v>407.48550229</v>
       </c>
     </row>
@@ -16573,32 +16544,22 @@
       <c r="B19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3">
+      <c r="E19">
         <v>1.2640449439999999</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19">
         <v>72.099999999999994</v>
       </c>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3">
+      <c r="M19">
         <v>11.043392577000001</v>
       </c>
-      <c r="N19" s="3">
+      <c r="N19">
         <v>304.27</v>
       </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3">
+      <c r="Q19">
         <v>2.172563625</v>
       </c>
-      <c r="R19" s="3">
+      <c r="R19">
         <v>390.85000114600001</v>
       </c>
     </row>
@@ -16606,32 +16567,22 @@
       <c r="B20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3">
+      <c r="E20">
         <v>1.2569832400000001</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20">
         <v>72.5</v>
       </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3">
+      <c r="M20">
         <v>0.710328654</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20">
         <v>296.32</v>
       </c>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3">
+      <c r="Q20">
         <v>2.1591610120000002</v>
       </c>
-      <c r="R20" s="3">
+      <c r="R20">
         <v>372.946472906</v>
       </c>
     </row>
@@ -16639,32 +16590,22 @@
       <c r="B21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3">
+      <c r="E21">
         <v>0.69832402199999999</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21">
         <v>72.099999999999994</v>
       </c>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3">
+      <c r="M21">
         <v>-7.5357659540000004</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21">
         <v>287.61</v>
       </c>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3">
+      <c r="Q21">
         <v>2.0935960589999998</v>
       </c>
-      <c r="R21" s="3">
+      <c r="R21">
         <v>354.96615412699998</v>
       </c>
     </row>
@@ -16672,32 +16613,22 @@
       <c r="B22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3">
+      <c r="E22">
         <v>0.553250346</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22">
         <v>72.7</v>
       </c>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3">
+      <c r="M22">
         <v>-2.3348427919999999</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22">
         <v>304.10000000000002</v>
       </c>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3">
+      <c r="Q22">
         <v>2.0656136090000001</v>
       </c>
-      <c r="R22" s="3">
+      <c r="R22">
         <v>377.08402116300005</v>
       </c>
     </row>
@@ -16705,32 +16636,22 @@
       <c r="B23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3">
+      <c r="E23">
         <v>0.83217753100000003</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23">
         <v>72.7</v>
       </c>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3">
+      <c r="M23">
         <v>3.503467315</v>
       </c>
-      <c r="N23" s="3">
+      <c r="N23">
         <v>314.93</v>
       </c>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3">
+      <c r="Q23">
         <v>2.12636695</v>
       </c>
-      <c r="R23" s="3">
+      <c r="R23">
         <v>394.09201179600001</v>
       </c>
     </row>
@@ -16738,32 +16659,22 @@
       <c r="B24" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3">
+      <c r="E24">
         <v>0.96551724100000003</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24">
         <v>73.2</v>
       </c>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3">
+      <c r="M24">
         <v>7.7652537800000001</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24">
         <v>319.33</v>
       </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3">
+      <c r="Q24">
         <v>2.1135265699999999</v>
       </c>
-      <c r="R24" s="3">
+      <c r="R24">
         <v>403.37429759099996</v>
       </c>
     </row>
@@ -16771,32 +16682,22 @@
       <c r="B25" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3">
+      <c r="E25">
         <v>0.97087378599999996</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25">
         <v>72.8</v>
       </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3">
+      <c r="M25">
         <v>34.616320711999997</v>
       </c>
-      <c r="N25" s="3">
+      <c r="N25">
         <v>387.17</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3">
+      <c r="Q25">
         <v>1.869722557</v>
       </c>
-      <c r="R25" s="3">
+      <c r="R25">
         <v>497.42691705499999</v>
       </c>
     </row>
@@ -16804,32 +16705,22 @@
       <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3">
+      <c r="E26">
         <v>1.5130674</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26">
         <v>73.8</v>
       </c>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3">
+      <c r="M26">
         <v>-13.04505097</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26">
         <v>264.43</v>
       </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3">
+      <c r="Q26">
         <v>2.2619047619999999</v>
       </c>
-      <c r="R26" s="3">
+      <c r="R26">
         <v>328.95992119199997</v>
       </c>
     </row>
@@ -16837,32 +16728,22 @@
       <c r="B27" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3">
+      <c r="E27">
         <v>1.5130674</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27">
         <v>73.8</v>
       </c>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3">
+      <c r="M27">
         <v>-7.87794113</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27">
         <v>290.12</v>
       </c>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3">
+      <c r="Q27">
         <v>2.3795359899999999</v>
       </c>
-      <c r="R27" s="3">
+      <c r="R27">
         <v>359.93466226000004</v>
       </c>
     </row>
@@ -16870,32 +16751,22 @@
       <c r="B28" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3">
+      <c r="E28">
         <v>0.95628415300000003</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28">
         <v>73.900000000000006</v>
       </c>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3">
+      <c r="M28">
         <v>-8.9468574830000005</v>
       </c>
-      <c r="N28" s="3">
+      <c r="N28">
         <v>290.76</v>
       </c>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3">
+      <c r="Q28">
         <v>1.9515079829999999</v>
       </c>
-      <c r="R28" s="3">
+      <c r="R28">
         <v>358.62093465300001</v>
       </c>
     </row>
@@ -16903,32 +16774,22 @@
       <c r="B29" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3">
+      <c r="E29">
         <v>1.5109890109999999</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29">
         <v>73.900000000000006</v>
       </c>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3">
+      <c r="M29">
         <v>-20.701500632999998</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29">
         <v>307.02</v>
       </c>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3">
+      <c r="Q29">
         <v>2.368265246</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29">
         <v>364.09775362400001</v>
       </c>
     </row>
@@ -16936,32 +16797,22 @@
       <c r="B30" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3">
+      <c r="E30">
         <v>0.94850948499999999</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30">
         <v>74.5</v>
       </c>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3">
+      <c r="M30">
         <v>16.650909503000001</v>
       </c>
-      <c r="N30" s="3">
+      <c r="N30">
         <v>308.45999999999998</v>
       </c>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3">
+      <c r="Q30">
         <v>1.862630966</v>
       </c>
-      <c r="R30" s="3">
+      <c r="R30">
         <v>402.42204995399993</v>
       </c>
     </row>
@@ -16969,32 +16820,22 @@
       <c r="B31" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3">
+      <c r="E31">
         <v>1.0840108399999999</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31">
         <v>74.599999999999994</v>
       </c>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3">
+      <c r="M31">
         <v>5.7769198949999998</v>
       </c>
-      <c r="N31" s="3">
+      <c r="N31">
         <v>306.88</v>
       </c>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3">
+      <c r="Q31">
         <v>1.9755955839999999</v>
       </c>
-      <c r="R31" s="3">
+      <c r="R31">
         <v>390.31652631900005</v>
       </c>
     </row>
@@ -17002,32 +16843,22 @@
       <c r="B32" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3">
+      <c r="E32">
         <v>1.4884979700000001</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32">
         <v>75</v>
       </c>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3">
+      <c r="M32">
         <v>3.5252441879999998</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32">
         <v>301.01</v>
       </c>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3">
+      <c r="Q32">
         <v>2.6102088170000002</v>
       </c>
-      <c r="R32" s="3">
+      <c r="R32">
         <v>383.633950975</v>
       </c>
     </row>
@@ -17035,32 +16866,22 @@
       <c r="B33" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3">
+      <c r="E33">
         <v>1.4884979700000001</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33">
         <v>75</v>
       </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3">
+      <c r="M33">
         <v>-5.1788157119999996</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33">
         <v>291.12</v>
       </c>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3">
+      <c r="Q33">
         <v>2.8918449970000002</v>
       </c>
-      <c r="R33" s="3">
+      <c r="R33">
         <v>365.32152725500003</v>
       </c>
     </row>
@@ -17068,32 +16889,22 @@
       <c r="B34" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3">
+      <c r="E34">
         <v>1.342281879</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34">
         <v>75.5</v>
       </c>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3">
+      <c r="M34">
         <v>-2.697270311</v>
       </c>
-      <c r="N34" s="3">
+      <c r="N34">
         <v>300.14</v>
       </c>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3">
+      <c r="Q34">
         <v>2.914285714</v>
       </c>
-      <c r="R34" s="3">
+      <c r="R34">
         <v>377.19929728199997</v>
       </c>
     </row>
@@ -17101,32 +16912,22 @@
       <c r="B35" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3">
+      <c r="E35">
         <v>1.3404825739999999</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35">
         <v>75.599999999999994</v>
       </c>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3">
+      <c r="M35">
         <v>-2.538451512</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35">
         <v>299.08999999999997</v>
       </c>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3">
+      <c r="Q35">
         <v>2.8490028490000001</v>
       </c>
-      <c r="R35" s="3">
+      <c r="R35">
         <v>376.34103391099995</v>
       </c>
     </row>
@@ -17134,32 +16935,22 @@
       <c r="B36" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3">
+      <c r="E36">
         <v>1.3333333329999999</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36">
         <v>76</v>
       </c>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3">
+      <c r="M36">
         <v>-0.647819009</v>
       </c>
-      <c r="N36" s="3">
+      <c r="N36">
         <v>299.06</v>
       </c>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3">
+      <c r="Q36">
         <v>2.6003391749999998</v>
       </c>
-      <c r="R36" s="3">
+      <c r="R36">
         <v>378.34585349899999</v>
       </c>
     </row>
@@ -17167,32 +16958,22 @@
       <c r="B37" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3">
+      <c r="E37">
         <v>1.2</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37">
         <v>75.900000000000006</v>
       </c>
-      <c r="G37" s="3"/>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3">
+      <c r="M37">
         <v>0.41907117300000002</v>
       </c>
-      <c r="N37" s="3">
+      <c r="N37">
         <v>292.33999999999997</v>
       </c>
-      <c r="O37" s="3"/>
-      <c r="P37" s="3"/>
-      <c r="Q37" s="3">
+      <c r="Q37">
         <v>2.304665542</v>
       </c>
-      <c r="R37" s="3">
+      <c r="R37">
         <v>372.16373671499997</v>
       </c>
     </row>
@@ -17200,32 +16981,22 @@
       <c r="B38" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3">
+      <c r="E38">
         <v>1.324503311</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38">
         <v>76.5</v>
       </c>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3">
+      <c r="M38">
         <v>-1.75917905</v>
       </c>
-      <c r="N38" s="3">
+      <c r="N38">
         <v>294.86</v>
       </c>
-      <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3">
+      <c r="Q38">
         <v>2.1654636310000002</v>
       </c>
-      <c r="R38" s="3">
+      <c r="R38">
         <v>373.09078789200004</v>
       </c>
     </row>
@@ -17233,32 +17004,22 @@
       <c r="B39" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3">
+      <c r="E39">
         <v>1.3227513230000001</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39">
         <v>76.599999999999994</v>
       </c>
-      <c r="G39" s="3"/>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3">
+      <c r="M39">
         <v>-1.5814637730000001</v>
       </c>
-      <c r="N39" s="3">
+      <c r="N39">
         <v>294.36</v>
       </c>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3">
+      <c r="Q39">
         <v>2.1052631580000001</v>
       </c>
-      <c r="R39" s="3">
+      <c r="R39">
         <v>372.80655070800003</v>
       </c>
     </row>
@@ -17266,32 +17027,22 @@
       <c r="B40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3">
+      <c r="E40">
         <v>1.447368421</v>
       </c>
-      <c r="F40" s="3">
+      <c r="F40">
         <v>77.099999999999994</v>
       </c>
-      <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3">
+      <c r="M40">
         <v>-1.324149</v>
       </c>
-      <c r="N40" s="3">
+      <c r="N40">
         <v>295.10000000000002</v>
       </c>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3">
+      <c r="Q40">
         <v>2.2589531680000001</v>
       </c>
-      <c r="R40" s="3">
+      <c r="R40">
         <v>374.58217258899998</v>
       </c>
     </row>
@@ -17299,32 +17050,22 @@
       <c r="B41" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3">
+      <c r="E41">
         <v>1.8445322790000001</v>
       </c>
-      <c r="F41" s="3">
+      <c r="F41">
         <v>77.3</v>
       </c>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3">
+      <c r="M41">
         <v>-2.2268591369999999</v>
       </c>
-      <c r="N41" s="3">
+      <c r="N41">
         <v>285.83</v>
       </c>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3">
+      <c r="Q41">
         <v>2.1978021980000002</v>
       </c>
-      <c r="R41" s="3">
+      <c r="R41">
         <v>364.94547533999997</v>
       </c>
     </row>
@@ -17332,32 +17073,22 @@
       <c r="B42" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3">
+      <c r="E42">
         <v>1.9607843140000001</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F42">
         <v>78</v>
       </c>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3">
+      <c r="M42">
         <v>-47.585294716</v>
       </c>
-      <c r="N42" s="3">
+      <c r="N42">
         <v>154.55000000000001</v>
       </c>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3">
+      <c r="Q42">
         <v>2.2282608700000002</v>
       </c>
-      <c r="R42" s="3">
+      <c r="R42">
         <v>189.15375046800003</v>
       </c>
     </row>
@@ -17365,32 +17096,22 @@
       <c r="B43" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C43" s="3"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3">
+      <c r="E43">
         <v>2.3498694520000001</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F43">
         <v>78.400000000000006</v>
       </c>
-      <c r="G43" s="3"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3">
+      <c r="M43">
         <v>-15.433482809999999</v>
       </c>
-      <c r="N43" s="3">
+      <c r="N43">
         <v>248.93</v>
       </c>
-      <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
-      <c r="Q43" s="3">
+      <c r="Q43">
         <v>2.3874118289999999</v>
       </c>
-      <c r="R43" s="3">
+      <c r="R43">
         <v>316.63379847099998</v>
       </c>
     </row>
@@ -17398,32 +17119,22 @@
       <c r="B44" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3">
+      <c r="E44">
         <v>2.2049286640000001</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44">
         <v>78.8</v>
       </c>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3">
+      <c r="M44">
         <v>18.092172144999999</v>
       </c>
-      <c r="N44" s="3">
+      <c r="N44">
         <v>348.49</v>
       </c>
-      <c r="O44" s="3"/>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3">
+      <c r="Q44">
         <v>2.2629310340000002</v>
       </c>
-      <c r="R44" s="3">
+      <c r="R44">
         <v>449.85003184300001</v>
       </c>
     </row>
@@ -17431,32 +17142,22 @@
       <c r="B45" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3">
+      <c r="E45">
         <v>1.811125485</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45">
         <v>78.7</v>
       </c>
-      <c r="G45" s="3"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3">
+      <c r="M45">
         <v>53.577301192999997</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45">
         <v>438.97</v>
       </c>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-      <c r="Q45" s="3">
+      <c r="Q45">
         <v>2.2043010750000001</v>
       </c>
-      <c r="R45" s="3">
+      <c r="R45">
         <v>575.26272775300004</v>
       </c>
     </row>
@@ -17464,32 +17165,22 @@
       <c r="B46" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3">
+      <c r="E46">
         <v>2.307692308</v>
       </c>
-      <c r="F46" s="3">
+      <c r="F46">
         <v>79.8</v>
       </c>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3">
+      <c r="M46">
         <v>185.73924296300001</v>
       </c>
-      <c r="N46" s="3">
+      <c r="N46">
         <v>441.61</v>
       </c>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3">
+      <c r="Q46">
         <v>2.8176501859999998</v>
       </c>
-      <c r="R46" s="3">
+      <c r="R46">
         <v>712.27458545700006</v>
       </c>
     </row>
@@ -17497,32 +17188,22 @@
       <c r="B47" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3">
+      <c r="E47">
         <v>2.423469388</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47">
         <v>80.3</v>
       </c>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3">
+      <c r="M47">
         <v>33.836821596</v>
       </c>
-      <c r="N47" s="3">
+      <c r="N47">
         <v>333.16</v>
       </c>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3">
+      <c r="Q47">
         <v>3.2326444090000002</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47">
         <v>452.95293539300002</v>
       </c>
     </row>
@@ -17530,32 +17211,22 @@
       <c r="B48" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3">
+      <c r="E48">
         <v>2.6649746190000001</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F48">
         <v>80.900000000000006</v>
       </c>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3">
+      <c r="M48">
         <v>-22.755315791000001</v>
       </c>
-      <c r="N48" s="3">
+      <c r="N48">
         <v>269.19</v>
       </c>
-      <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="3">
+      <c r="Q48">
         <v>3.4773445729999999</v>
       </c>
-      <c r="R48" s="3">
+      <c r="R48">
         <v>333.47700340099999</v>
       </c>
     </row>
@@ -17563,32 +17234,22 @@
       <c r="B49" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3">
+      <c r="E49">
         <v>2.9224904700000001</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F49">
         <v>81</v>
       </c>
-      <c r="G49" s="3"/>
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3">
+      <c r="M49">
         <v>-24.393466524000001</v>
       </c>
-      <c r="N49" s="3">
+      <c r="N49">
         <v>331.89</v>
       </c>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3">
+      <c r="Q49">
         <v>3.7348763809999999</v>
       </c>
-      <c r="R49" s="3">
+      <c r="R49">
         <v>395.15390032699997</v>
       </c>
     </row>
@@ -17596,32 +17257,22 @@
       <c r="B50" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3">
+      <c r="E50">
         <v>2.5062656639999998</v>
       </c>
-      <c r="F50" s="3">
+      <c r="F50">
         <v>81.8</v>
       </c>
-      <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3">
+      <c r="M50">
         <v>-28.156065305999999</v>
       </c>
-      <c r="N50" s="3">
+      <c r="N50">
         <v>317.27</v>
       </c>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3">
+      <c r="Q50">
         <v>3.4126163389999999</v>
       </c>
-      <c r="R50" s="3">
+      <c r="R50">
         <v>376.832816697</v>
       </c>
     </row>
@@ -17629,32 +17280,22 @@
       <c r="B51" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3">
+      <c r="E51">
         <v>1.7434620169999999</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F51">
         <v>81.7</v>
       </c>
-      <c r="G51" s="3"/>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3">
+      <c r="M51">
         <v>-7.5549285629999998</v>
       </c>
-      <c r="N51" s="3">
+      <c r="N51">
         <v>307.99</v>
       </c>
-      <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
-      <c r="Q51" s="3">
+      <c r="Q51">
         <v>2.72073922</v>
       </c>
-      <c r="R51" s="3">
+      <c r="R51">
         <v>386.59927267400002</v>
       </c>
     </row>
@@ -17662,32 +17303,22 @@
       <c r="B52" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3">
+      <c r="E52">
         <v>2.101359703</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52">
         <v>82.6</v>
       </c>
-      <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3">
+      <c r="M52">
         <v>14.350458784000001</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52">
         <v>307.82</v>
       </c>
-      <c r="O52" s="3"/>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3">
+      <c r="Q52">
         <v>3.1059063139999998</v>
       </c>
-      <c r="R52" s="3">
+      <c r="R52">
         <v>409.97772480099997</v>
       </c>
     </row>
@@ -17695,32 +17326,22 @@
       <c r="B53" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3">
+      <c r="E53">
         <v>2.3757201650000002</v>
       </c>
-      <c r="F53" s="3">
+      <c r="F53">
         <v>82.924333333000007</v>
       </c>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3">
+      <c r="M53">
         <v>-16.975503931999999</v>
       </c>
-      <c r="N53" s="3">
+      <c r="N53">
         <v>275.55</v>
       </c>
-      <c r="O53" s="3"/>
-      <c r="P53" s="3"/>
-      <c r="Q53" s="3">
+      <c r="Q53">
         <v>3.4989858009999999</v>
       </c>
-      <c r="R53" s="3">
+      <c r="R53">
         <v>347.37353536700004</v>
       </c>
     </row>
@@ -17728,32 +17349,22 @@
       <c r="B54" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
-      <c r="E54" s="3">
+      <c r="E54">
         <v>3.4197229010000001</v>
       </c>
-      <c r="F54" s="3">
+      <c r="F54">
         <v>84.597333332999995</v>
       </c>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3">
+      <c r="M54">
         <v>-22.750338828</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54">
         <v>245.09</v>
       </c>
-      <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3">
+      <c r="Q54">
         <v>4.3833333330000004</v>
       </c>
-      <c r="R54" s="3">
+      <c r="R54">
         <v>314.74005073900003</v>
       </c>
     </row>
@@ -17761,32 +17372,22 @@
       <c r="B55" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3">
+      <c r="E55">
         <v>4.8388412890000003</v>
       </c>
-      <c r="F55" s="3">
+      <c r="F55">
         <v>85.653333333000006</v>
       </c>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3">
+      <c r="M55">
         <v>-16.698594109999998</v>
       </c>
-      <c r="N55" s="3">
+      <c r="N55">
         <v>256.56</v>
       </c>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
-      <c r="Q55" s="3">
+      <c r="Q55">
         <v>5.3473263370000002</v>
       </c>
-      <c r="R55" s="3">
+      <c r="R55">
         <v>335.70090684900003</v>
       </c>
     </row>
@@ -17794,32 +17395,22 @@
       <c r="B56" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C56" s="3"/>
-      <c r="D56" s="3"/>
-      <c r="E56" s="3">
+      <c r="E56">
         <v>3.8240516549999999</v>
       </c>
-      <c r="F56" s="3">
+      <c r="F56">
         <v>85.758666667</v>
       </c>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3">
+      <c r="M56">
         <v>-20.037684361</v>
       </c>
-      <c r="N56" s="3">
+      <c r="N56">
         <v>246.14</v>
       </c>
-      <c r="O56" s="3"/>
-      <c r="P56" s="3"/>
-      <c r="Q56" s="3">
+      <c r="Q56">
         <v>3.7860082300000002</v>
       </c>
-      <c r="R56" s="3">
+      <c r="R56">
         <v>319.47104219099998</v>
       </c>
     </row>
@@ -17827,32 +17418,22 @@
       <c r="B57" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3">
+      <c r="E57">
         <v>3.005551246</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57">
         <v>85.416666667000001</v>
       </c>
-      <c r="G57" s="3"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3">
+      <c r="M57">
         <v>-7.987661042</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57">
         <v>253.54</v>
       </c>
-      <c r="O57" s="3"/>
-      <c r="P57" s="3"/>
-      <c r="Q57" s="3">
+      <c r="Q57">
         <v>2.3844520660000001</v>
       </c>
-      <c r="R57" s="3">
+      <c r="R57">
         <v>336.359008937</v>
       </c>
     </row>
@@ -17860,32 +17441,22 @@
       <c r="B58" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3">
+      <c r="E58">
         <v>2.088718321</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58">
         <v>86.364333333000005</v>
       </c>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="3"/>
-      <c r="M58" s="3">
+      <c r="M58">
         <v>11.587580073</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58">
         <v>273.49</v>
       </c>
-      <c r="O58" s="3"/>
-      <c r="P58" s="3"/>
-      <c r="Q58" s="3">
+      <c r="Q58">
         <v>1.4370110169999999</v>
       </c>
-      <c r="R58" s="3">
+      <c r="R58">
         <v>374.96764274399999</v>
       </c>
     </row>
@@ -17893,32 +17464,22 @@
       <c r="B59" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3">
+      <c r="E59">
         <v>1.4897260269999999</v>
       </c>
-      <c r="F59" s="3">
+      <c r="F59">
         <v>86.929333333000002</v>
       </c>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3">
+      <c r="M59">
         <v>7.397879638</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59">
         <v>275.54000000000002</v>
       </c>
-      <c r="O59" s="3"/>
-      <c r="P59" s="3"/>
-      <c r="Q59" s="3">
+      <c r="Q59">
         <v>1.312460468</v>
       </c>
-      <c r="R59" s="3">
+      <c r="R59">
         <v>372.66939946600002</v>
       </c>
     </row>
@@ -17926,34 +17487,25 @@
       <c r="B60" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3">
+      <c r="E60">
         <v>2.1031887930000002</v>
       </c>
-      <c r="F60" s="3">
+      <c r="F60">
         <v>87.562333332999998</v>
       </c>
-      <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3">
+      <c r="L60">
         <v>290.83999999999997</v>
       </c>
-      <c r="M60" s="3">
+      <c r="M60">
         <v>18.160396521999999</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60">
         <v>290.83999999999997</v>
       </c>
-      <c r="O60" s="3"/>
-      <c r="P60" s="3"/>
-      <c r="Q60" s="3">
+      <c r="Q60">
         <v>2.7914353690000002</v>
       </c>
-      <c r="R60" s="3">
+      <c r="R60">
         <v>692.29735401699998</v>
       </c>
     </row>
@@ -17961,34 +17513,25 @@
       <c r="B61" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3">
+      <c r="E61">
         <v>3.2745365849999999</v>
       </c>
-      <c r="F61" s="3">
+      <c r="F61">
         <v>88.213666666999998</v>
       </c>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3">
+      <c r="L61">
         <v>310.977755</v>
       </c>
-      <c r="M61" s="3">
+      <c r="M61">
         <v>-13.51791946</v>
       </c>
-      <c r="N61" s="3">
+      <c r="N61">
         <v>219.26666700000001</v>
       </c>
-      <c r="O61" s="3"/>
-      <c r="P61" s="3"/>
-      <c r="Q61" s="3">
+      <c r="Q61">
         <v>4.5461796139999997</v>
       </c>
-      <c r="R61" s="3">
+      <c r="R61">
         <v>612.76088540600006</v>
       </c>
     </row>
@@ -17996,34 +17539,25 @@
       <c r="B62" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3">
+      <c r="E62">
         <v>3.4566738579999998</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62">
         <v>89.349666666999994</v>
       </c>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3">
+      <c r="L62">
         <v>263.107056</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62">
         <v>-18.278547662000001</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62">
         <v>223.5</v>
       </c>
-      <c r="O62" s="3"/>
-      <c r="P62" s="3"/>
-      <c r="Q62" s="3">
+      <c r="Q62">
         <v>5.1629151579999997</v>
       </c>
-      <c r="R62" s="3">
+      <c r="R62">
         <v>566.29776402100003</v>
       </c>
     </row>
@@ -18031,34 +17565,25 @@
       <c r="B63" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3">
+      <c r="E63">
         <v>3.0852646589999999</v>
       </c>
-      <c r="F63" s="3">
+      <c r="F63">
         <v>89.611333333000005</v>
       </c>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3">
+      <c r="L63">
         <v>279.28384599999998</v>
       </c>
-      <c r="M63" s="3">
+      <c r="M63">
         <v>-18.535723669999999</v>
       </c>
-      <c r="N63" s="3">
+      <c r="N63">
         <v>224.466667</v>
       </c>
-      <c r="O63" s="3"/>
-      <c r="P63" s="3"/>
-      <c r="Q63" s="3">
+      <c r="Q63">
         <v>4.6823786480000003</v>
       </c>
-      <c r="R63" s="3">
+      <c r="R63">
         <v>582.59376597000005</v>
       </c>
     </row>
@@ -18066,34 +17591,25 @@
       <c r="B64" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3">
+      <c r="E64">
         <v>3.3762614819999999</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F64">
         <v>90.518666667000005</v>
       </c>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3">
+      <c r="L64">
         <v>296.90782999999999</v>
       </c>
-      <c r="M64" s="3">
+      <c r="M64">
         <v>-21.950213175999998</v>
       </c>
-      <c r="N64" s="3">
+      <c r="N64">
         <v>227</v>
       </c>
-      <c r="O64" s="3"/>
-      <c r="P64" s="3"/>
-      <c r="Q64" s="3">
+      <c r="Q64">
         <v>4.6597747260000002</v>
       </c>
-      <c r="R64" s="3">
+      <c r="R64">
         <v>600.51231969900005</v>
       </c>
     </row>
@@ -18101,34 +17617,25 @@
       <c r="B65" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3">
+      <c r="E65">
         <v>4.1184094680000003</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F65">
         <v>91.846666666999994</v>
       </c>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3">
+      <c r="L65">
         <v>302.59850699999998</v>
       </c>
-      <c r="M65" s="3">
+      <c r="M65">
         <v>5.3207658779999996</v>
       </c>
-      <c r="N65" s="3">
+      <c r="N65">
         <v>230.933333</v>
       </c>
-      <c r="O65" s="3"/>
-      <c r="P65" s="3"/>
-      <c r="Q65" s="3">
+      <c r="Q65">
         <v>5.3402502289999996</v>
       </c>
-      <c r="R65" s="3">
+      <c r="R65">
         <v>640.15793224200002</v>
       </c>
     </row>
@@ -18136,34 +17643,25 @@
       <c r="B66" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3">
+      <c r="E66">
         <v>4.3771847680000002</v>
       </c>
-      <c r="F66" s="3">
+      <c r="F66">
         <v>93.260666666999995</v>
       </c>
-      <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3">
+      <c r="L66">
         <v>306.34029099999998</v>
       </c>
-      <c r="M66" s="3">
+      <c r="M66">
         <v>5.1155852350000002</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66">
         <v>234.933333</v>
       </c>
-      <c r="O66" s="3"/>
-      <c r="P66" s="3"/>
-      <c r="Q66" s="3">
+      <c r="Q66">
         <v>5.178865439</v>
       </c>
-      <c r="R66" s="3">
+      <c r="R66">
         <v>649.20592610900007</v>
       </c>
     </row>
@@ -18171,34 +17669,25 @@
       <c r="B67" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3">
+      <c r="E67">
         <v>4.7058779770000001</v>
       </c>
-      <c r="F67" s="3">
+      <c r="F67">
         <v>93.828333333000003</v>
       </c>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3">
+      <c r="L67">
         <v>311.12984799999998</v>
       </c>
-      <c r="M67" s="3">
+      <c r="M67">
         <v>5.2420549369999998</v>
       </c>
-      <c r="N67" s="3">
+      <c r="N67">
         <v>236.23333299999999</v>
       </c>
-      <c r="O67" s="3"/>
-      <c r="P67" s="3"/>
-      <c r="Q67" s="3">
+      <c r="Q67">
         <v>5.3526166689999997</v>
       </c>
-      <c r="R67" s="3">
+      <c r="R67">
         <v>656.49206391599989</v>
       </c>
     </row>
@@ -18206,34 +17695,25 @@
       <c r="B68" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3">
+      <c r="E68">
         <v>4.64581891</v>
       </c>
-      <c r="F68" s="3">
+      <c r="F68">
         <v>94.724000000000004</v>
       </c>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3">
+      <c r="L68">
         <v>316.85687899999999</v>
       </c>
-      <c r="M68" s="3">
+      <c r="M68">
         <v>5.1248163</v>
       </c>
-      <c r="N68" s="3">
+      <c r="N68">
         <v>238.63333299999999</v>
       </c>
-      <c r="O68" s="3"/>
-      <c r="P68" s="3"/>
-      <c r="Q68" s="3">
+      <c r="Q68">
         <v>5.2779006339999999</v>
       </c>
-      <c r="R68" s="3">
+      <c r="R68">
         <v>665.26274784400005</v>
       </c>
     </row>
@@ -18241,36 +17721,28 @@
       <c r="B69" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3">
+      <c r="E69">
         <v>3.4902373519999998</v>
       </c>
-      <c r="F69" s="3">
+      <c r="F69">
         <v>95.052333333000007</v>
       </c>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-      <c r="J69" s="3">
+      <c r="J69">
         <v>79.8</v>
       </c>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3">
+      <c r="L69">
         <v>323.353565</v>
       </c>
-      <c r="M69" s="3">
+      <c r="M69">
         <v>3.7384529500000001</v>
       </c>
-      <c r="N69" s="3">
+      <c r="N69">
         <v>239.566667</v>
       </c>
-      <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
-      <c r="Q69" s="3">
+      <c r="Q69">
         <v>3.8238702199999999</v>
       </c>
-      <c r="R69" s="3">
+      <c r="R69">
         <v>748.82512585500001</v>
       </c>
     </row>
@@ -18278,36 +17750,28 @@
       <c r="B70" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-      <c r="E70" s="3">
+      <c r="E70">
         <v>2.7553595299999998</v>
       </c>
-      <c r="F70" s="3">
+      <c r="F70">
         <v>95.830333332999999</v>
       </c>
-      <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-      <c r="J70" s="3">
+      <c r="J70">
         <v>79.900000000000006</v>
       </c>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3">
+      <c r="L70">
         <v>329.535349</v>
       </c>
-      <c r="M70" s="3">
+      <c r="M70">
         <v>3.1072644770000002</v>
       </c>
-      <c r="N70" s="3">
+      <c r="N70">
         <v>242.23333299999999</v>
       </c>
-      <c r="O70" s="3"/>
-      <c r="P70" s="3"/>
-      <c r="Q70" s="3">
+      <c r="Q70">
         <v>3.1450120959999999</v>
       </c>
-      <c r="R70" s="3">
+      <c r="R70">
         <v>756.50665143599997</v>
       </c>
     </row>
@@ -18315,36 +17779,28 @@
       <c r="B71" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-      <c r="E71" s="3">
+      <c r="E71">
         <v>2.412561948</v>
       </c>
-      <c r="F71" s="3">
+      <c r="F71">
         <v>96.091999999999999</v>
       </c>
-      <c r="G71" s="3"/>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
-      <c r="J71" s="3">
+      <c r="J71">
         <v>80.3</v>
       </c>
-      <c r="K71" s="3"/>
-      <c r="L71" s="3">
+      <c r="L71">
         <v>335.70624099999998</v>
       </c>
-      <c r="M71" s="3">
+      <c r="M71">
         <v>2.9067307790000001</v>
       </c>
-      <c r="N71" s="3">
+      <c r="N71">
         <v>243.1</v>
       </c>
-      <c r="O71" s="3"/>
-      <c r="P71" s="3"/>
-      <c r="Q71" s="3">
+      <c r="Q71">
         <v>2.9012170959999999</v>
       </c>
-      <c r="R71" s="3">
+      <c r="R71">
         <v>763.41875082299998</v>
       </c>
     </row>
@@ -18352,36 +17808,28 @@
       <c r="B72" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-      <c r="E72" s="3">
+      <c r="E72">
         <v>2.6698619149999998</v>
       </c>
-      <c r="F72" s="3">
+      <c r="F72">
         <v>97.253</v>
       </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-      <c r="J72" s="3">
+      <c r="J72">
         <v>80.8</v>
       </c>
-      <c r="K72" s="3"/>
-      <c r="L72" s="3">
+      <c r="L72">
         <v>341.43751600000002</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72">
         <v>3.0870234710000002</v>
       </c>
-      <c r="N72" s="3">
+      <c r="N72">
         <v>246</v>
       </c>
-      <c r="O72" s="3"/>
-      <c r="P72" s="3"/>
-      <c r="Q72" s="3">
+      <c r="Q72">
         <v>3.0107828040000002</v>
       </c>
-      <c r="R72" s="3">
+      <c r="R72">
         <v>774.25818418999995</v>
       </c>
     </row>
@@ -18389,38 +17837,31 @@
       <c r="B73" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3">
+      <c r="E73">
         <v>2.7763653009999998</v>
       </c>
-      <c r="F73" s="3">
+      <c r="F73">
         <v>97.691333333000003</v>
       </c>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3">
+      <c r="I73">
         <v>2.130325815</v>
       </c>
-      <c r="J73" s="3">
+      <c r="J73">
         <v>81.5</v>
       </c>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3">
+      <c r="L73">
         <v>347.24930000000001</v>
       </c>
-      <c r="M73" s="3">
+      <c r="M73">
         <v>3.255878665</v>
       </c>
-      <c r="N73" s="3">
+      <c r="N73">
         <v>247.36666700000001</v>
       </c>
-      <c r="O73" s="3"/>
-      <c r="P73" s="3"/>
-      <c r="Q73" s="3">
+      <c r="Q73">
         <v>3.2366071430000001</v>
       </c>
-      <c r="R73" s="3">
+      <c r="R73">
         <v>785.20647725699996</v>
       </c>
     </row>
@@ -18428,38 +17869,31 @@
       <c r="B74" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-      <c r="E74" s="3">
+      <c r="E74">
         <v>2.6793882240000002</v>
       </c>
-      <c r="F74" s="3">
+      <c r="F74">
         <v>98.397999999999996</v>
       </c>
-      <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3">
+      <c r="I74">
         <v>2.1276595739999999</v>
       </c>
-      <c r="J74" s="3">
+      <c r="J74">
         <v>81.599999999999994</v>
       </c>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3">
+      <c r="L74">
         <v>352.52330899999998</v>
       </c>
-      <c r="M74" s="3">
+      <c r="M74">
         <v>3.0961882529999998</v>
       </c>
-      <c r="N74" s="3">
+      <c r="N74">
         <v>249.73333299999999</v>
       </c>
-      <c r="O74" s="3"/>
-      <c r="P74" s="3"/>
-      <c r="Q74" s="3">
+      <c r="Q74">
         <v>3.062913907</v>
       </c>
-      <c r="R74" s="3">
+      <c r="R74">
         <v>793.22079195800006</v>
       </c>
     </row>
@@ -18467,38 +17901,31 @@
       <c r="B75" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3"/>
-      <c r="E75" s="3">
+      <c r="E75">
         <v>2.70886234</v>
       </c>
-      <c r="F75" s="3">
+      <c r="F75">
         <v>98.694999999999993</v>
       </c>
-      <c r="G75" s="3"/>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3">
+      <c r="I75">
         <v>2.3661270239999999</v>
       </c>
-      <c r="J75" s="3">
+      <c r="J75">
         <v>82.2</v>
       </c>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3">
+      <c r="L75">
         <v>356.99577199999999</v>
       </c>
-      <c r="M75" s="3">
+      <c r="M75">
         <v>3.1948445080000001</v>
       </c>
-      <c r="N75" s="3">
+      <c r="N75">
         <v>250.86666700000001</v>
       </c>
-      <c r="O75" s="3"/>
-      <c r="P75" s="3"/>
-      <c r="Q75" s="3">
+      <c r="Q75">
         <v>3.218264338</v>
       </c>
-      <c r="R75" s="3">
+      <c r="R75">
         <v>800.24553720999995</v>
       </c>
     </row>
@@ -18506,38 +17933,31 @@
       <c r="B76" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-      <c r="E76" s="3">
+      <c r="E76">
         <v>2.1027628969999999</v>
       </c>
-      <c r="F76" s="3">
+      <c r="F76">
         <v>99.298000000000002</v>
       </c>
-      <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3">
+      <c r="I76">
         <v>1.8564356440000001</v>
       </c>
-      <c r="J76" s="3">
+      <c r="J76">
         <v>82.3</v>
       </c>
-      <c r="K76" s="3"/>
-      <c r="L76" s="3">
+      <c r="L76">
         <v>360.877634</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M76">
         <v>2.6287264229999998</v>
       </c>
-      <c r="N76" s="3">
+      <c r="N76">
         <v>252.466667</v>
       </c>
-      <c r="O76" s="3"/>
-      <c r="P76" s="3"/>
-      <c r="Q76" s="3">
+      <c r="Q76">
         <v>2.7052746060000001</v>
       </c>
-      <c r="R76" s="3">
+      <c r="R76">
         <v>804.23550057</v>
       </c>
     </row>
@@ -18545,38 +17965,31 @@
       <c r="B77" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3">
+      <c r="E77">
         <v>1.7391512039999999</v>
       </c>
-      <c r="F77" s="3">
+      <c r="F77">
         <v>99.390333333000001</v>
       </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3">
+      <c r="I77">
         <v>1.349693252</v>
       </c>
-      <c r="J77" s="3">
+      <c r="J77">
         <v>82.6</v>
       </c>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3">
+      <c r="L77">
         <v>364.24172199999998</v>
       </c>
-      <c r="M77" s="3">
+      <c r="M77">
         <v>2.6276782070000002</v>
       </c>
-      <c r="N77" s="3">
+      <c r="N77">
         <v>253.86666700000001</v>
       </c>
-      <c r="O77" s="3"/>
-      <c r="P77" s="3"/>
-      <c r="Q77" s="3">
+      <c r="Q77">
         <v>2.675675676</v>
       </c>
-      <c r="R77" s="3">
+      <c r="R77">
         <v>808.4909206719999</v>
       </c>
     </row>
@@ -18584,38 +17997,31 @@
       <c r="B78" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3">
+      <c r="E78">
         <v>1.720563426</v>
       </c>
-      <c r="F78" s="3">
+      <c r="F78">
         <v>100.09099999999999</v>
       </c>
-      <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3">
+      <c r="I78">
         <v>1.1029411760000001</v>
       </c>
-      <c r="J78" s="3">
+      <c r="J78">
         <v>82.5</v>
       </c>
-      <c r="K78" s="3"/>
-      <c r="L78" s="3">
+      <c r="L78">
         <v>367.12964699999998</v>
       </c>
-      <c r="M78" s="3">
+      <c r="M78">
         <v>2.4959959989999998</v>
       </c>
-      <c r="N78" s="3">
+      <c r="N78">
         <v>255.966667</v>
       </c>
-      <c r="O78" s="3"/>
-      <c r="P78" s="3"/>
-      <c r="Q78" s="3">
+      <c r="Q78">
         <v>2.597054886</v>
       </c>
-      <c r="R78" s="3">
+      <c r="R78">
         <v>813.603869487</v>
       </c>
     </row>
@@ -18623,38 +18029,31 @@
       <c r="B79" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C79" s="3"/>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3">
+      <c r="E79">
         <v>1.456000811</v>
       </c>
-      <c r="F79" s="3">
+      <c r="F79">
         <v>100.13200000000001</v>
       </c>
-      <c r="G79" s="3"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3">
+      <c r="I79">
         <v>1.581508516</v>
       </c>
-      <c r="J79" s="3">
+      <c r="J79">
         <v>83.5</v>
       </c>
-      <c r="K79" s="3"/>
-      <c r="L79" s="3">
+      <c r="L79">
         <v>369.26654500000001</v>
       </c>
-      <c r="M79" s="3">
+      <c r="M79">
         <v>2.3917087399999999</v>
       </c>
-      <c r="N79" s="3">
+      <c r="N79">
         <v>256.86666700000001</v>
       </c>
-      <c r="O79" s="3"/>
-      <c r="P79" s="3"/>
-      <c r="Q79" s="3">
+      <c r="Q79">
         <v>2.4783477679999999</v>
       </c>
-      <c r="R79" s="3">
+      <c r="R79">
         <v>817.67277783500003</v>
       </c>
     </row>
@@ -18662,38 +18061,31 @@
       <c r="B80" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3">
+      <c r="E80">
         <v>0.93523199499999998</v>
       </c>
-      <c r="F80" s="3">
+      <c r="F80">
         <v>100.226666667</v>
       </c>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3">
+      <c r="I80">
         <v>1.215066829</v>
       </c>
-      <c r="J80" s="3">
+      <c r="J80">
         <v>83.3</v>
       </c>
-      <c r="K80" s="3"/>
-      <c r="L80" s="3">
+      <c r="L80">
         <v>370.92641099999997</v>
       </c>
-      <c r="M80" s="3">
+      <c r="M80">
         <v>1.9672561369999999</v>
       </c>
-      <c r="N80" s="3">
+      <c r="N80">
         <v>257.433333</v>
       </c>
-      <c r="O80" s="3"/>
-      <c r="P80" s="3"/>
-      <c r="Q80" s="3">
+      <c r="Q80">
         <v>2.0251489079999998</v>
       </c>
-      <c r="R80" s="3">
+      <c r="R80">
         <v>818.02911453600007</v>
       </c>
     </row>
@@ -18701,38 +18093,31 @@
       <c r="B81" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3">
+      <c r="E81">
         <v>0.100613406</v>
       </c>
-      <c r="F81" s="3">
+      <c r="F81">
         <v>99.490333332999995</v>
       </c>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3">
+      <c r="I81">
         <v>0.96852300199999997</v>
       </c>
-      <c r="J81" s="3">
+      <c r="J81">
         <v>83.4</v>
       </c>
-      <c r="K81" s="3"/>
-      <c r="L81" s="3">
+      <c r="L81">
         <v>372.71173199999998</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81">
         <v>0.99789902699999999</v>
       </c>
-      <c r="N81" s="3">
+      <c r="N81">
         <v>256.39999999999998</v>
       </c>
-      <c r="O81" s="3"/>
-      <c r="P81" s="3"/>
-      <c r="Q81" s="3">
+      <c r="Q81">
         <v>1.026585944</v>
       </c>
-      <c r="R81" s="3">
+      <c r="R81">
         <v>815.09568671199997</v>
       </c>
     </row>
@@ -18740,36 +18125,28 @@
       <c r="B82" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-      <c r="E82" s="3">
+      <c r="E82">
         <v>-1.6651513999999999E-2</v>
       </c>
-      <c r="F82" s="3">
+      <c r="F82">
         <v>100.074333333</v>
       </c>
-      <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="3">
+      <c r="I82">
         <v>0.84848484800000001</v>
       </c>
-      <c r="J82" s="3">
+      <c r="J82">
         <v>83.2</v>
       </c>
-      <c r="K82" s="3"/>
-      <c r="L82" s="3"/>
-      <c r="M82" s="3">
+      <c r="M82">
         <v>0.97668967200000001</v>
       </c>
-      <c r="N82" s="3">
+      <c r="N82">
         <v>258.46666699999997</v>
       </c>
-      <c r="O82" s="3"/>
-      <c r="P82" s="3"/>
-      <c r="Q82" s="3">
+      <c r="Q82">
         <v>1.0046972860000001</v>
       </c>
-      <c r="R82" s="3">
+      <c r="R82">
         <v>444.55422062499997</v>
       </c>
     </row>
@@ -18777,36 +18154,28 @@
       <c r="B83" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3">
+      <c r="E83">
         <v>9.653923E-3</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83">
         <v>100.141666667</v>
       </c>
-      <c r="G83" s="3"/>
-      <c r="H83" s="3"/>
-      <c r="I83" s="3">
+      <c r="I83">
         <v>0</v>
       </c>
-      <c r="J83" s="3">
+      <c r="J83">
         <v>83.5</v>
       </c>
-      <c r="K83" s="3"/>
-      <c r="L83" s="3"/>
-      <c r="M83" s="3">
+      <c r="M83">
         <v>0.96029042200000003</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83">
         <v>259.33333299999998</v>
       </c>
-      <c r="O83" s="3"/>
-      <c r="P83" s="3"/>
-      <c r="Q83" s="3">
+      <c r="Q83">
         <v>1.02717462</v>
       </c>
-      <c r="R83" s="3">
+      <c r="R83">
         <v>444.97211863199999</v>
       </c>
     </row>
@@ -18814,36 +18183,28 @@
       <c r="B84" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3">
+      <c r="E84">
         <v>6.7181056000000003E-2</v>
       </c>
-      <c r="F84" s="3">
+      <c r="F84">
         <v>100.294</v>
       </c>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3">
+      <c r="I84">
         <v>0.72028811500000001</v>
       </c>
-      <c r="J84" s="3">
+      <c r="J84">
         <v>83.9</v>
       </c>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3"/>
-      <c r="M84" s="3">
+      <c r="M84">
         <v>0.98407380700000002</v>
       </c>
-      <c r="N84" s="3">
+      <c r="N84">
         <v>259.96666699999997</v>
       </c>
-      <c r="O84" s="3"/>
-      <c r="P84" s="3"/>
-      <c r="Q84" s="3">
+      <c r="Q84">
         <v>1.0508562530000001</v>
       </c>
-      <c r="R84" s="3">
+      <c r="R84">
         <v>446.98306623099995</v>
       </c>
     </row>
@@ -18851,36 +18212,28 @@
       <c r="B85" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-      <c r="E85" s="3">
+      <c r="E85">
         <v>0.34676735800000003</v>
       </c>
-      <c r="F85" s="3">
+      <c r="F85">
         <v>99.835333332999994</v>
       </c>
-      <c r="G85" s="3"/>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3">
+      <c r="I85">
         <v>1.1990407670000001</v>
       </c>
-      <c r="J85" s="3">
+      <c r="J85">
         <v>84.4</v>
       </c>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3"/>
-      <c r="M85" s="3">
+      <c r="M85">
         <v>1.3910557720000001</v>
       </c>
-      <c r="N85" s="3">
+      <c r="N85">
         <v>259.96666699999997</v>
       </c>
-      <c r="O85" s="3"/>
-      <c r="P85" s="3"/>
-      <c r="Q85" s="3">
+      <c r="Q85">
         <v>1.4721208960000001</v>
       </c>
-      <c r="R85" s="3">
+      <c r="R85">
         <v>448.61098512599995</v>
       </c>
     </row>
@@ -18888,36 +18241,28 @@
       <c r="B86" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3">
+      <c r="E86">
         <v>0.35140545499999998</v>
       </c>
-      <c r="F86" s="3">
+      <c r="F86">
         <v>100.426</v>
       </c>
-      <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="3">
+      <c r="I86">
         <v>1.682692308</v>
       </c>
-      <c r="J86" s="3">
+      <c r="J86">
         <v>84.6</v>
       </c>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
-      <c r="M86" s="3">
+      <c r="M86">
         <v>1.444415655</v>
       </c>
-      <c r="N86" s="3">
+      <c r="N86">
         <v>262.2</v>
       </c>
-      <c r="O86" s="3"/>
-      <c r="P86" s="3"/>
-      <c r="Q86" s="3">
+      <c r="Q86">
         <v>1.5243508589999999</v>
       </c>
-      <c r="R86" s="3">
+      <c r="R86">
         <v>452.22886427699996</v>
       </c>
     </row>
@@ -18925,36 +18270,28 @@
       <c r="B87" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3">
+      <c r="E87">
         <v>0.72630440200000002</v>
       </c>
-      <c r="F87" s="3">
+      <c r="F87">
         <v>100.869</v>
       </c>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3">
+      <c r="I87">
         <v>2.395209581</v>
       </c>
-      <c r="J87" s="3">
+      <c r="J87">
         <v>85.5</v>
       </c>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3"/>
-      <c r="M87" s="3">
+      <c r="M87">
         <v>1.889460157</v>
       </c>
-      <c r="N87" s="3">
+      <c r="N87">
         <v>264.23333300000002</v>
       </c>
-      <c r="O87" s="3"/>
-      <c r="P87" s="3"/>
-      <c r="Q87" s="3">
+      <c r="Q87">
         <v>2.007722008</v>
       </c>
-      <c r="R87" s="3">
+      <c r="R87">
         <v>457.62102914799999</v>
       </c>
     </row>
@@ -18962,36 +18299,28 @@
       <c r="B88" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3">
+      <c r="E88">
         <v>1.2111060149999999</v>
       </c>
-      <c r="F88" s="3">
+      <c r="F88">
         <v>101.508666667</v>
       </c>
-      <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="3">
+      <c r="I88">
         <v>2.6221692490000001</v>
       </c>
-      <c r="J88" s="3">
+      <c r="J88">
         <v>86.1</v>
       </c>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3"/>
-      <c r="M88" s="3">
+      <c r="M88">
         <v>2.2438772889999998</v>
       </c>
-      <c r="N88" s="3">
+      <c r="N88">
         <v>265.8</v>
       </c>
-      <c r="O88" s="3"/>
-      <c r="P88" s="3"/>
-      <c r="Q88" s="3">
+      <c r="Q88">
         <v>2.4778533829999998</v>
       </c>
-      <c r="R88" s="3">
+      <c r="R88">
         <v>461.96367260300002</v>
       </c>
     </row>
@@ -18999,36 +18328,28 @@
       <c r="B89" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3">
+      <c r="E89">
         <v>2.1435296789999998</v>
       </c>
-      <c r="F89" s="3">
+      <c r="F89">
         <v>101.97533333299999</v>
       </c>
-      <c r="G89" s="3"/>
-      <c r="H89" s="3"/>
-      <c r="I89" s="3">
+      <c r="I89">
         <v>2.3696682459999998</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89">
         <v>86.4</v>
       </c>
-      <c r="K89" s="3"/>
-      <c r="L89" s="3"/>
-      <c r="M89" s="3">
+      <c r="M89">
         <v>2.9875622480000001</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89">
         <v>267.73333300000002</v>
       </c>
-      <c r="O89" s="3"/>
-      <c r="P89" s="3"/>
-      <c r="Q89" s="3">
+      <c r="Q89">
         <v>3.2610091149999998</v>
       </c>
-      <c r="R89" s="3">
+      <c r="R89">
         <v>466.87043562099996</v>
       </c>
     </row>
@@ -19036,36 +18357,28 @@
       <c r="B90" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3">
+      <c r="E90">
         <v>2.742981565</v>
       </c>
-      <c r="F90" s="3">
+      <c r="F90">
         <v>103.180666667</v>
       </c>
-      <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3">
+      <c r="I90">
         <v>2.2458628840000001</v>
       </c>
-      <c r="J90" s="3">
+      <c r="J90">
         <v>86.5</v>
       </c>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
-      <c r="M90" s="3">
+      <c r="M90">
         <v>3.5596235699999998</v>
       </c>
-      <c r="N90" s="3">
+      <c r="N90">
         <v>271.53333300000003</v>
       </c>
-      <c r="O90" s="3"/>
-      <c r="P90" s="3"/>
-      <c r="Q90" s="3">
+      <c r="Q90">
         <v>3.8300038170000001</v>
       </c>
-      <c r="R90" s="3">
+      <c r="R90">
         <v>473.59247150300001</v>
       </c>
     </row>
@@ -19073,36 +18386,28 @@
       <c r="B91" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-      <c r="E91" s="3">
+      <c r="E91">
         <v>2.8168548649999998</v>
       </c>
-      <c r="F91" s="3">
+      <c r="F91">
         <v>103.71033333299999</v>
       </c>
-      <c r="G91" s="3"/>
-      <c r="H91" s="3"/>
-      <c r="I91" s="3">
+      <c r="I91">
         <v>1.2865497079999999</v>
       </c>
-      <c r="J91" s="3">
+      <c r="J91">
         <v>86.6</v>
       </c>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3"/>
-      <c r="M91" s="3">
+      <c r="M91">
         <v>3.7845338759999998</v>
       </c>
-      <c r="N91" s="3">
+      <c r="N91">
         <v>274.23333300000002</v>
       </c>
-      <c r="O91" s="3"/>
-      <c r="P91" s="3"/>
-      <c r="Q91" s="3">
+      <c r="Q91">
         <v>4.0247287409999997</v>
       </c>
-      <c r="R91" s="3">
+      <c r="R91">
         <v>476.45633352300001</v>
       </c>
     </row>
@@ -19110,36 +18415,28 @@
       <c r="B92" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3">
+      <c r="E92">
         <v>3.0217452699999998</v>
       </c>
-      <c r="F92" s="3">
+      <c r="F92">
         <v>104.57599999999999</v>
       </c>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3">
+      <c r="I92">
         <v>1.5098722419999999</v>
       </c>
-      <c r="J92" s="3">
+      <c r="J92">
         <v>87.4</v>
       </c>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3"/>
-      <c r="M92" s="3">
+      <c r="M92">
         <v>3.987960873</v>
       </c>
-      <c r="N92" s="3">
+      <c r="N92">
         <v>276.39999999999998</v>
       </c>
-      <c r="O92" s="3"/>
-      <c r="P92" s="3"/>
-      <c r="Q92" s="3">
+      <c r="Q92">
         <v>4.0967176150000002</v>
       </c>
-      <c r="R92" s="3">
+      <c r="R92">
         <v>480.99229599999995</v>
       </c>
     </row>
@@ -19147,36 +18444,28 @@
       <c r="B93" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-      <c r="E93" s="3">
+      <c r="E93">
         <v>2.7176506740000002</v>
       </c>
-      <c r="F93" s="3">
+      <c r="F93">
         <v>104.746666667</v>
       </c>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3">
+      <c r="I93">
         <v>1.273148148</v>
       </c>
-      <c r="J93" s="3">
+      <c r="J93">
         <v>87.5</v>
       </c>
-      <c r="K93" s="3"/>
-      <c r="L93" s="3"/>
-      <c r="M93" s="3">
+      <c r="M93">
         <v>3.6354584210000001</v>
       </c>
-      <c r="N93" s="3">
+      <c r="N93">
         <v>277.46666699999997</v>
       </c>
-      <c r="O93" s="3"/>
-      <c r="P93" s="3"/>
-      <c r="Q93" s="3">
+      <c r="Q93">
         <v>3.6802188240000002</v>
       </c>
-      <c r="R93" s="3">
+      <c r="R93">
         <v>481.01980973399998</v>
       </c>
     </row>
@@ -19184,36 +18473,28 @@
       <c r="B94" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-      <c r="E94" s="3">
+      <c r="E94">
         <v>2.4164733699999998</v>
       </c>
-      <c r="F94" s="3">
+      <c r="F94">
         <v>105.67400000000001</v>
       </c>
-      <c r="G94" s="3"/>
-      <c r="H94" s="3"/>
-      <c r="I94" s="3">
+      <c r="I94">
         <v>1.849710983</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94">
         <v>88.1</v>
       </c>
-      <c r="K94" s="3"/>
-      <c r="L94" s="3"/>
-      <c r="M94" s="3">
+      <c r="M94">
         <v>3.351338084</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94">
         <v>280.63333299999999</v>
       </c>
-      <c r="O94" s="3"/>
-      <c r="P94" s="3"/>
-      <c r="Q94" s="3">
+      <c r="Q94">
         <v>3.3823529410000002</v>
       </c>
-      <c r="R94" s="3">
+      <c r="R94">
         <v>485.40720837800001</v>
       </c>
     </row>
@@ -19221,36 +18502,28 @@
       <c r="B95" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-      <c r="E95" s="3">
+      <c r="E95">
         <v>2.5153391979999999</v>
       </c>
-      <c r="F95" s="3">
+      <c r="F95">
         <v>106.319</v>
       </c>
-      <c r="G95" s="3"/>
-      <c r="H95" s="3"/>
-      <c r="I95" s="3">
+      <c r="I95">
         <v>2.3094688219999999</v>
       </c>
-      <c r="J95" s="3">
+      <c r="J95">
         <v>88.6</v>
       </c>
-      <c r="K95" s="3"/>
-      <c r="L95" s="3"/>
-      <c r="M95" s="3">
+      <c r="M95">
         <v>3.318342049</v>
       </c>
-      <c r="N95" s="3">
+      <c r="N95">
         <v>283.33333299999998</v>
       </c>
-      <c r="O95" s="3"/>
-      <c r="P95" s="3"/>
-      <c r="Q95" s="3">
+      <c r="Q95">
         <v>3.2989690719999998</v>
       </c>
-      <c r="R95" s="3">
+      <c r="R95">
         <v>489.69445214099994</v>
       </c>
     </row>
@@ -19258,36 +18531,28 @@
       <c r="B96" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-      <c r="E96" s="3">
+      <c r="E96">
         <v>2.2682068540000002</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96">
         <v>106.94799999999999</v>
       </c>
-      <c r="G96" s="3"/>
-      <c r="H96" s="3"/>
-      <c r="I96" s="3">
+      <c r="I96">
         <v>2.1739130430000002</v>
       </c>
-      <c r="J96" s="3">
+      <c r="J96">
         <v>89.3</v>
       </c>
-      <c r="K96" s="3"/>
-      <c r="L96" s="3"/>
-      <c r="M96" s="3">
+      <c r="M96">
         <v>3.0752532559999999</v>
       </c>
-      <c r="N96" s="3">
+      <c r="N96">
         <v>284.89999999999998</v>
       </c>
-      <c r="O96" s="3"/>
-      <c r="P96" s="3"/>
-      <c r="Q96" s="3">
+      <c r="Q96">
         <v>3.008785654</v>
       </c>
-      <c r="R96" s="3">
+      <c r="R96">
         <v>491.67415880699997</v>
       </c>
     </row>
@@ -19295,36 +18560,28 @@
       <c r="B97" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3">
+      <c r="E97">
         <v>1.875</v>
       </c>
-      <c r="F97" s="3">
+      <c r="F97">
         <v>106.710666667</v>
       </c>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3">
+      <c r="I97">
         <v>2.0571428570000001</v>
       </c>
-      <c r="J97" s="3">
+      <c r="J97">
         <v>89.3</v>
       </c>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
-      <c r="M97" s="3">
+      <c r="M97">
         <v>2.486785196</v>
       </c>
-      <c r="N97" s="3">
+      <c r="N97">
         <v>284.36666700000001</v>
       </c>
-      <c r="O97" s="3"/>
-      <c r="P97" s="3"/>
-      <c r="Q97" s="3">
+      <c r="Q97">
         <v>2.4463364909999998</v>
       </c>
-      <c r="R97" s="3">
+      <c r="R97">
         <v>489.24259821099997</v>
       </c>
     </row>
@@ -19332,36 +18589,28 @@
       <c r="B98" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3">
+      <c r="E98">
         <v>2.0478074080000002</v>
       </c>
-      <c r="F98" s="3">
+      <c r="F98">
         <v>107.83799999999999</v>
       </c>
-      <c r="G98" s="3"/>
-      <c r="H98" s="3"/>
-      <c r="I98" s="3">
+      <c r="I98">
         <v>2.3836549379999998</v>
       </c>
-      <c r="J98" s="3">
+      <c r="J98">
         <v>90.2</v>
       </c>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3"/>
-      <c r="M98" s="3">
+      <c r="M98">
         <v>2.9813518270000001</v>
       </c>
-      <c r="N98" s="3">
+      <c r="N98">
         <v>289</v>
       </c>
-      <c r="O98" s="3"/>
-      <c r="P98" s="3"/>
-      <c r="Q98" s="3">
+      <c r="Q98">
         <v>2.9397818870000001</v>
       </c>
-      <c r="R98" s="3">
+      <c r="R98">
         <v>497.39059606000001</v>
       </c>
     </row>
@@ -19369,36 +18618,28 @@
       <c r="B99" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3"/>
-      <c r="E99" s="3">
+      <c r="E99">
         <v>1.832848942</v>
       </c>
-      <c r="F99" s="3">
+      <c r="F99">
         <v>108.267666667</v>
       </c>
-      <c r="G99" s="3"/>
-      <c r="H99" s="3"/>
-      <c r="I99" s="3">
+      <c r="I99">
         <v>2.257336343</v>
       </c>
-      <c r="J99" s="3">
+      <c r="J99">
         <v>90.6</v>
       </c>
-      <c r="K99" s="3"/>
-      <c r="L99" s="3"/>
-      <c r="M99" s="3">
+      <c r="M99">
         <v>2.611764709</v>
       </c>
-      <c r="N99" s="3">
+      <c r="N99">
         <v>290.73333300000002</v>
       </c>
-      <c r="O99" s="3"/>
-      <c r="P99" s="3"/>
-      <c r="Q99" s="3">
+      <c r="Q99">
         <v>2.5830691560000001</v>
       </c>
-      <c r="R99" s="3">
+      <c r="R99">
         <v>498.88601881700004</v>
       </c>
     </row>
@@ -19406,36 +18647,28 @@
       <c r="B100" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-      <c r="E100" s="3">
+      <c r="E100">
         <v>1.413459501</v>
       </c>
-      <c r="F100" s="3">
+      <c r="F100">
         <v>108.45966666699999</v>
       </c>
-      <c r="G100" s="3"/>
-      <c r="H100" s="3"/>
-      <c r="I100" s="3">
+      <c r="I100">
         <v>2.015677492</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100">
         <v>91.1</v>
       </c>
-      <c r="K100" s="3"/>
-      <c r="L100" s="3"/>
-      <c r="M100" s="3">
+      <c r="M100">
         <v>2.1762021759999999</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100">
         <v>291.10000000000002</v>
       </c>
-      <c r="O100" s="3"/>
-      <c r="P100" s="3"/>
-      <c r="Q100" s="3">
+      <c r="Q100">
         <v>2.2198855009999998</v>
       </c>
-      <c r="R100" s="3">
+      <c r="R100">
         <v>498.48489133700002</v>
       </c>
     </row>
@@ -19443,36 +18676,28 @@
       <c r="B101" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3">
+      <c r="E101">
         <v>1.6671248110000001</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101">
         <v>108.48966666699999</v>
       </c>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="3">
+      <c r="I101">
         <v>2.911534155</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101">
         <v>91.9</v>
       </c>
-      <c r="K101" s="3"/>
-      <c r="L101" s="3"/>
-      <c r="M101" s="3">
+      <c r="M101">
         <v>2.5905518669999998</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101">
         <v>291.73333300000002</v>
       </c>
-      <c r="O101" s="3"/>
-      <c r="P101" s="3"/>
-      <c r="Q101" s="3">
+      <c r="Q101">
         <v>2.668851691</v>
       </c>
-      <c r="R101" s="3">
+      <c r="R101">
         <v>501.961062191</v>
       </c>
     </row>
@@ -19480,36 +18705,28 @@
       <c r="B102" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-      <c r="E102" s="3">
+      <c r="E102">
         <v>0.61666573899999999</v>
       </c>
-      <c r="F102" s="3">
+      <c r="F102">
         <v>108.503</v>
       </c>
-      <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
-      <c r="I102" s="3">
+      <c r="I102">
         <v>9.5343680709999994</v>
       </c>
-      <c r="J102" s="3">
+      <c r="J102">
         <v>98.8</v>
       </c>
-      <c r="K102" s="3"/>
-      <c r="L102" s="3"/>
-      <c r="M102" s="3">
+      <c r="M102">
         <v>1.211072664</v>
       </c>
-      <c r="N102" s="3">
+      <c r="N102">
         <v>292.5</v>
       </c>
-      <c r="O102" s="3"/>
-      <c r="P102" s="3"/>
-      <c r="Q102" s="3">
+      <c r="Q102">
         <v>1.3818516810000001</v>
       </c>
-      <c r="R102" s="3">
+      <c r="R102">
         <v>512.54695815499997</v>
       </c>
     </row>
@@ -19517,36 +18734,28 @@
       <c r="B103" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-      <c r="E103" s="3">
+      <c r="E103">
         <v>0.59666936599999998</v>
       </c>
-      <c r="F103" s="3">
+      <c r="F103">
         <v>108.913666667</v>
       </c>
-      <c r="G103" s="3"/>
-      <c r="H103" s="3"/>
-      <c r="I103" s="3">
+      <c r="I103">
         <v>4.7461368650000004</v>
       </c>
-      <c r="J103" s="3">
+      <c r="J103">
         <v>94.9</v>
       </c>
-      <c r="K103" s="3"/>
-      <c r="L103" s="3"/>
-      <c r="M103" s="3">
+      <c r="M103">
         <v>1.100664986</v>
       </c>
-      <c r="N103" s="3">
+      <c r="N103">
         <v>293.933333</v>
       </c>
-      <c r="O103" s="3"/>
-      <c r="P103" s="3"/>
-      <c r="Q103" s="3">
+      <c r="Q103">
         <v>1.3391324250000001</v>
       </c>
-      <c r="R103" s="3">
+      <c r="R103">
         <v>505.52960330899998</v>
       </c>
     </row>
@@ -19554,36 +18763,28 @@
       <c r="B104" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
-      <c r="E104" s="3">
+      <c r="E104">
         <v>0.53353166600000002</v>
       </c>
-      <c r="F104" s="3">
+      <c r="F104">
         <v>109.038333333</v>
       </c>
-      <c r="G104" s="3"/>
-      <c r="H104" s="3"/>
-      <c r="I104" s="3">
+      <c r="I104">
         <v>3.5126234909999998</v>
       </c>
-      <c r="J104" s="3">
+      <c r="J104">
         <v>94.3</v>
       </c>
-      <c r="K104" s="3"/>
-      <c r="L104" s="3"/>
-      <c r="M104" s="3">
+      <c r="M104">
         <v>1.1336310549999999</v>
       </c>
-      <c r="N104" s="3">
+      <c r="N104">
         <v>294.39999999999998</v>
       </c>
-      <c r="O104" s="3"/>
-      <c r="P104" s="3"/>
-      <c r="Q104" s="3">
+      <c r="Q104">
         <v>1.360155446</v>
       </c>
-      <c r="R104" s="3">
+      <c r="R104">
         <v>504.27827499099999</v>
       </c>
     </row>
@@ -19591,36 +18792,28 @@
       <c r="B105" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
-      <c r="E105" s="3">
+      <c r="E105">
         <v>0.609581865</v>
       </c>
-      <c r="F105" s="3">
+      <c r="F105">
         <v>109.151</v>
       </c>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
-      <c r="I105" s="3">
+      <c r="I105">
         <v>3.6996735580000002</v>
       </c>
-      <c r="J105" s="3">
+      <c r="J105">
         <v>95.3</v>
       </c>
-      <c r="K105" s="3"/>
-      <c r="L105" s="3"/>
-      <c r="M105" s="3">
+      <c r="M105">
         <v>1.405393055</v>
       </c>
-      <c r="N105" s="3">
+      <c r="N105">
         <v>295.83333299999998</v>
       </c>
-      <c r="O105" s="3"/>
-      <c r="P105" s="3"/>
-      <c r="Q105" s="3">
+      <c r="Q105">
         <v>1.596169194</v>
       </c>
-      <c r="R105" s="3">
+      <c r="R105">
         <v>507.59515067199999</v>
       </c>
     </row>
@@ -19628,36 +18821,28 @@
       <c r="B106" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
-      <c r="E106" s="3">
+      <c r="E106">
         <v>2.0518633890000002</v>
       </c>
-      <c r="F106" s="3">
+      <c r="F106">
         <v>110.729333333</v>
       </c>
-      <c r="G106" s="3"/>
-      <c r="H106" s="3"/>
-      <c r="I106" s="3">
+      <c r="I106">
         <v>-4.9595141700000003</v>
       </c>
-      <c r="J106" s="3">
+      <c r="J106">
         <v>93.9</v>
       </c>
-      <c r="K106" s="3"/>
-      <c r="L106" s="3"/>
-      <c r="M106" s="3">
+      <c r="M106">
         <v>3.3618232479999999</v>
       </c>
-      <c r="N106" s="3">
+      <c r="N106">
         <v>302.33333299999998</v>
       </c>
-      <c r="O106" s="3"/>
-      <c r="P106" s="3"/>
-      <c r="Q106" s="3">
+      <c r="Q106">
         <v>3.509768287</v>
       </c>
-      <c r="R106" s="3">
+      <c r="R106">
         <v>510.92660708699998</v>
       </c>
     </row>
@@ -19665,36 +18850,28 @@
       <c r="B107" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3"/>
-      <c r="E107" s="3">
+      <c r="E107">
         <v>2.771614214</v>
       </c>
-      <c r="F107" s="3">
+      <c r="F107">
         <v>111.932333333</v>
       </c>
-      <c r="G107" s="3"/>
-      <c r="H107" s="3"/>
-      <c r="I107" s="3">
+      <c r="I107">
         <v>-0.42149631199999998</v>
       </c>
-      <c r="J107" s="3">
+      <c r="J107">
         <v>94.5</v>
       </c>
-      <c r="K107" s="3"/>
-      <c r="L107" s="3"/>
-      <c r="M107" s="3">
+      <c r="M107">
         <v>4.5021549160000003</v>
       </c>
-      <c r="N107" s="3">
+      <c r="N107">
         <v>307.16666700000002</v>
       </c>
-      <c r="O107" s="3"/>
-      <c r="P107" s="3"/>
-      <c r="Q107" s="3">
+      <c r="Q107">
         <v>4.5967924099999999</v>
       </c>
-      <c r="R107" s="3">
+      <c r="R107">
         <v>525.04806556100004</v>
       </c>
     </row>
@@ -19702,36 +18879,28 @@
       <c r="B108" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
-      <c r="E108" s="3">
+      <c r="E108">
         <v>4.9074484509999996</v>
       </c>
-      <c r="F108" s="3">
+      <c r="F108">
         <v>114.389333333</v>
       </c>
-      <c r="G108" s="3"/>
-      <c r="H108" s="3"/>
-      <c r="I108" s="3">
+      <c r="I108">
         <v>1.378579003</v>
       </c>
-      <c r="J108" s="3">
+      <c r="J108">
         <v>95.6</v>
       </c>
-      <c r="K108" s="3"/>
-      <c r="L108" s="3"/>
-      <c r="M108" s="3">
+      <c r="M108">
         <v>6.8840580840000003</v>
       </c>
-      <c r="N108" s="3">
+      <c r="N108">
         <v>314.66666700000002</v>
       </c>
-      <c r="O108" s="3"/>
-      <c r="P108" s="3"/>
-      <c r="Q108" s="3">
+      <c r="Q108">
         <v>7.0252593589999996</v>
       </c>
-      <c r="R108" s="3">
+      <c r="R108">
         <v>544.85134522999999</v>
       </c>
     </row>
@@ -19739,36 +18908,28 @@
       <c r="B109" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3">
+      <c r="E109">
         <v>6.2195185259999999</v>
       </c>
-      <c r="F109" s="3">
+      <c r="F109">
         <v>115.939666667</v>
       </c>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="3">
+      <c r="I109">
         <v>1.783840504</v>
       </c>
-      <c r="J109" s="3">
+      <c r="J109">
         <v>97</v>
       </c>
-      <c r="K109" s="3"/>
-      <c r="L109" s="3"/>
-      <c r="M109" s="3">
+      <c r="M109">
         <v>8.3267607980000005</v>
       </c>
-      <c r="N109" s="3">
+      <c r="N109">
         <v>320.46666699999997</v>
       </c>
-      <c r="O109" s="3"/>
-      <c r="P109" s="3"/>
-      <c r="Q109" s="3">
+      <c r="Q109">
         <v>8.4838963080000003</v>
       </c>
-      <c r="R109" s="3">
+      <c r="R109">
         <v>558.22034980299998</v>
       </c>
     </row>
@@ -19776,36 +18937,28 @@
       <c r="B110" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3">
+      <c r="E110">
         <v>9.1692053900000001</v>
       </c>
-      <c r="F110" s="3">
+      <c r="F110">
         <v>120.88233333300001</v>
       </c>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3">
+      <c r="I110">
         <v>5.5378061770000002</v>
       </c>
-      <c r="J110" s="3">
+      <c r="J110">
         <v>99.1</v>
       </c>
-      <c r="K110" s="3"/>
-      <c r="L110" s="3"/>
-      <c r="M110" s="3">
+      <c r="M110">
         <v>11.543550178</v>
       </c>
-      <c r="N110" s="3">
+      <c r="N110">
         <v>337.23333300000002</v>
       </c>
-      <c r="O110" s="3"/>
-      <c r="P110" s="3"/>
-      <c r="Q110" s="3">
+      <c r="Q110">
         <v>11.631734884</v>
       </c>
-      <c r="R110" s="3">
+      <c r="R110">
         <v>595.097962962</v>
       </c>
     </row>
@@ -19813,36 +18966,28 @@
       <c r="B111" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
-      <c r="E111" s="3">
+      <c r="E111">
         <v>10.022126462999999</v>
       </c>
-      <c r="F111" s="3">
+      <c r="F111">
         <v>123.15033333300001</v>
       </c>
-      <c r="G111" s="3"/>
-      <c r="H111" s="3"/>
-      <c r="I111" s="3">
+      <c r="I111">
         <v>6.560846561</v>
       </c>
-      <c r="J111" s="3">
+      <c r="J111">
         <v>100.7</v>
       </c>
-      <c r="K111" s="3"/>
-      <c r="L111" s="3"/>
-      <c r="M111" s="3">
+      <c r="M111">
         <v>12.42539315</v>
       </c>
-      <c r="N111" s="3">
+      <c r="N111">
         <v>345.33333299999998</v>
       </c>
-      <c r="O111" s="3"/>
-      <c r="P111" s="3"/>
-      <c r="Q111" s="3">
+      <c r="Q111">
         <v>12.320483748999999</v>
       </c>
-      <c r="R111" s="3">
+      <c r="R111">
         <v>610.51251625600003</v>
       </c>
     </row>
@@ -19850,36 +18995,28 @@
       <c r="B112" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
-      <c r="E112" s="3">
+      <c r="E112">
         <v>10.749545412</v>
       </c>
-      <c r="F112" s="3">
+      <c r="F112">
         <v>126.68566666700001</v>
       </c>
-      <c r="G112" s="3"/>
-      <c r="H112" s="3"/>
-      <c r="I112" s="3">
+      <c r="I112">
         <v>7.9497907950000002</v>
       </c>
-      <c r="J112" s="3">
+      <c r="J112">
         <v>103.2</v>
       </c>
-      <c r="K112" s="3"/>
-      <c r="L112" s="3"/>
-      <c r="M112" s="3">
+      <c r="M112">
         <v>13.866525303</v>
       </c>
-      <c r="N112" s="3">
+      <c r="N112">
         <v>358.3</v>
       </c>
-      <c r="O112" s="3"/>
-      <c r="P112" s="3"/>
-      <c r="Q112" s="3">
+      <c r="Q112">
         <v>13.423243072</v>
       </c>
-      <c r="R112" s="3">
+      <c r="R112">
         <v>634.17477124899995</v>
       </c>
     </row>
@@ -19887,36 +19024,28 @@
       <c r="B113" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
-      <c r="E113" s="3">
+      <c r="E113">
         <v>10.174832311999999</v>
       </c>
-      <c r="F113" s="3">
+      <c r="F113">
         <v>127.736333333</v>
       </c>
-      <c r="G113" s="3"/>
-      <c r="H113" s="3"/>
-      <c r="I113" s="3">
+      <c r="I113">
         <v>8.3505154640000008</v>
       </c>
-      <c r="J113" s="3">
+      <c r="J113">
         <v>105.1</v>
       </c>
-      <c r="K113" s="3"/>
-      <c r="L113" s="3"/>
-      <c r="M113" s="3">
+      <c r="M113">
         <v>13.584356029</v>
       </c>
-      <c r="N113" s="3">
+      <c r="N113">
         <v>364</v>
       </c>
-      <c r="O113" s="3"/>
-      <c r="P113" s="3"/>
-      <c r="Q113" s="3">
+      <c r="Q113">
         <v>12.703010240999999</v>
       </c>
-      <c r="R113" s="3">
+      <c r="R113">
         <v>641.64904737900008</v>
       </c>
     </row>
@@ -19924,36 +19053,28 @@
       <c r="B114" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3"/>
-      <c r="E114" s="3">
+      <c r="E114">
         <v>8.427754814</v>
       </c>
-      <c r="F114" s="3">
+      <c r="F114">
         <v>131.07</v>
       </c>
-      <c r="G114" s="3"/>
-      <c r="H114" s="3"/>
-      <c r="I114" s="3">
+      <c r="I114">
         <v>7.9717457109999996</v>
       </c>
-      <c r="J114" s="3">
+      <c r="J114">
         <v>107</v>
       </c>
-      <c r="K114" s="3"/>
-      <c r="L114" s="3"/>
-      <c r="M114" s="3">
+      <c r="M114">
         <v>11.149550272999999</v>
       </c>
-      <c r="N114" s="3">
+      <c r="N114">
         <v>374.83333299999998</v>
       </c>
-      <c r="O114" s="3"/>
-      <c r="P114" s="3"/>
-      <c r="Q114" s="3">
+      <c r="Q114">
         <v>10.085520495000001</v>
       </c>
-      <c r="R114" s="3">
+      <c r="R114">
         <v>650.537904293</v>
       </c>
     </row>
@@ -19961,36 +19082,28 @@
       <c r="B115" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
-      <c r="E115" s="3">
+      <c r="E115">
         <v>6.7118508270000001</v>
       </c>
-      <c r="F115" s="3">
+      <c r="F115">
         <v>131.416</v>
       </c>
-      <c r="G115" s="3"/>
-      <c r="H115" s="3"/>
-      <c r="I115" s="3">
+      <c r="I115">
         <v>7.2492552139999997</v>
       </c>
-      <c r="J115" s="3">
+      <c r="J115">
         <v>108</v>
       </c>
-      <c r="K115" s="3"/>
-      <c r="L115" s="3"/>
-      <c r="M115" s="3">
+      <c r="M115">
         <v>8.9961391010000007</v>
       </c>
-      <c r="N115" s="3">
+      <c r="N115">
         <v>376.4</v>
       </c>
-      <c r="O115" s="3"/>
-      <c r="P115" s="3"/>
-      <c r="Q115" s="3">
+      <c r="Q115">
         <v>7.7581234380000001</v>
       </c>
-      <c r="R115" s="3">
+      <c r="R115">
         <v>646.53136857999993</v>
       </c>
     </row>
@@ -19998,36 +19111,28 @@
       <c r="B116" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3">
+      <c r="E116">
         <v>4.1772681470000004</v>
       </c>
-      <c r="F116" s="3">
+      <c r="F116">
         <v>131.97766666699999</v>
       </c>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="3">
+      <c r="I116">
         <v>5.03875969</v>
       </c>
-      <c r="J116" s="3">
+      <c r="J116">
         <v>108.4</v>
       </c>
-      <c r="K116" s="3"/>
-      <c r="L116" s="3"/>
-      <c r="M116" s="3">
+      <c r="M116">
         <v>5.5074889760000003</v>
       </c>
-      <c r="N116" s="3">
+      <c r="N116">
         <v>378.03333300000003</v>
       </c>
-      <c r="O116" s="3"/>
-      <c r="P116" s="3"/>
-      <c r="Q116" s="3">
+      <c r="Q116">
         <v>4.3009753829999999</v>
       </c>
-      <c r="R116" s="3">
+      <c r="R116">
         <v>637.43549186300004</v>
       </c>
     </row>
@@ -20035,36 +19140,28 @@
       <c r="B117" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
-      <c r="E117" s="3">
+      <c r="E117">
         <v>3.5377561590000002</v>
       </c>
-      <c r="F117" s="3">
+      <c r="F117">
         <v>132.25533333300001</v>
       </c>
-      <c r="G117" s="3"/>
-      <c r="H117" s="3"/>
-      <c r="I117" s="3">
+      <c r="I117">
         <v>4.2816365369999998</v>
       </c>
-      <c r="J117" s="3">
+      <c r="J117">
         <v>109.6</v>
       </c>
-      <c r="K117" s="3"/>
-      <c r="L117" s="3"/>
-      <c r="M117" s="3">
+      <c r="M117">
         <v>4.5787546700000004</v>
       </c>
-      <c r="N117" s="3">
+      <c r="N117">
         <v>380.66666700000002</v>
       </c>
-      <c r="O117" s="3"/>
-      <c r="P117" s="3"/>
-      <c r="Q117" s="3">
+      <c r="Q117">
         <v>3.542909592</v>
       </c>
-      <c r="R117" s="3">
+      <c r="R117">
         <v>638.46305729100004</v>
       </c>
     </row>
@@ -20072,36 +19169,28 @@
       <c r="B118" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3">
+      <c r="E118">
         <v>2.0988784620000001</v>
       </c>
-      <c r="F118" s="3">
+      <c r="F118">
         <v>133.821</v>
       </c>
-      <c r="G118" s="3"/>
-      <c r="H118" s="3"/>
-      <c r="I118" s="3">
+      <c r="I118">
         <v>3.1775700929999999</v>
       </c>
-      <c r="J118" s="3">
+      <c r="J118">
         <v>110.4</v>
       </c>
-      <c r="K118" s="3"/>
-      <c r="L118" s="3"/>
-      <c r="M118" s="3">
+      <c r="M118">
         <v>3.0413517149999998</v>
       </c>
-      <c r="N118" s="3">
+      <c r="N118">
         <v>386.23333300000002</v>
       </c>
-      <c r="O118" s="3"/>
-      <c r="P118" s="3"/>
-      <c r="Q118" s="3">
+      <c r="Q118">
         <v>2.0716135370000002</v>
       </c>
-      <c r="R118" s="3">
+      <c r="R118">
         <v>640.843746807</v>
       </c>
     </row>
@@ -20109,36 +19198,28 @@
       <c r="B119" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3">
+      <c r="E119">
         <v>2.0428765649999998</v>
       </c>
-      <c r="F119" s="3">
+      <c r="F119">
         <v>134.10066666700001</v>
       </c>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3">
+      <c r="I119">
         <v>3.703703704</v>
       </c>
-      <c r="J119" s="3">
+      <c r="J119">
         <v>112</v>
       </c>
-      <c r="K119" s="3"/>
-      <c r="L119" s="3"/>
-      <c r="M119" s="3">
+      <c r="M119">
         <v>3.2589444740000002</v>
       </c>
-      <c r="N119" s="3">
+      <c r="N119">
         <v>388.66666700000002</v>
       </c>
-      <c r="O119" s="3"/>
-      <c r="P119" s="3"/>
-      <c r="Q119" s="3">
+      <c r="Q119">
         <v>2.5158354890000001</v>
       </c>
-      <c r="R119" s="3">
+      <c r="R119">
         <v>646.28869389900001</v>
       </c>
     </row>
@@ -20146,52 +19227,52 @@
       <c r="B120" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C120" s="3">
+      <c r="C120">
         <v>2.4685994849999999</v>
       </c>
-      <c r="D120" s="3">
+      <c r="D120">
         <v>135.235666667</v>
       </c>
-      <c r="E120" s="3">
+      <c r="E120">
         <v>2.4685994849999999</v>
       </c>
-      <c r="F120" s="3">
+      <c r="F120">
         <v>135.235666667</v>
       </c>
-      <c r="G120" s="3">
+      <c r="G120">
         <v>4.3357933580000001</v>
       </c>
-      <c r="H120" s="3">
+      <c r="H120">
         <v>113.1</v>
       </c>
-      <c r="I120" s="3">
+      <c r="I120">
         <v>4.3357933580000001</v>
       </c>
-      <c r="J120" s="3">
+      <c r="J120">
         <v>113.1</v>
       </c>
-      <c r="K120" s="3">
+      <c r="K120">
         <v>3.49175558</v>
       </c>
-      <c r="L120" s="3">
+      <c r="L120">
         <v>391.23333300000002</v>
       </c>
-      <c r="M120" s="3">
+      <c r="M120">
         <v>3.49175558</v>
       </c>
-      <c r="N120" s="3">
+      <c r="N120">
         <v>391.23333300000002</v>
       </c>
-      <c r="O120" s="3">
+      <c r="O120">
         <v>2.921268258</v>
       </c>
-      <c r="P120" s="3">
+      <c r="P120">
         <v>385.2</v>
       </c>
-      <c r="Q120" s="3">
+      <c r="Q120">
         <v>2.921268258</v>
       </c>
-      <c r="R120" s="3">
+      <c r="R120">
         <v>1690.7728326960003</v>
       </c>
     </row>
@@ -20199,38 +19280,31 @@
       <c r="B121" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C121" s="3">
+      <c r="C121">
         <v>2.7088726219999999</v>
       </c>
-      <c r="D121" s="3">
+      <c r="D121">
         <v>135.83796184900001</v>
       </c>
-      <c r="E121" s="3"/>
-      <c r="F121" s="3"/>
-      <c r="G121" s="3">
+      <c r="G121">
         <v>3.9761813030000002</v>
       </c>
-      <c r="H121" s="3">
+      <c r="H121">
         <v>113.957894708</v>
       </c>
-      <c r="I121" s="3"/>
-      <c r="J121" s="3"/>
-      <c r="K121" s="3">
+      <c r="K121">
         <v>3.4478595420000002</v>
       </c>
-      <c r="L121" s="3">
+      <c r="L121">
         <v>393.79151899999999</v>
       </c>
-      <c r="M121" s="3"/>
-      <c r="N121" s="3"/>
-      <c r="O121" s="3">
+      <c r="O121">
         <v>2.9829451549999999</v>
       </c>
-      <c r="P121" s="3">
+      <c r="P121">
         <v>387.25020143</v>
       </c>
-      <c r="Q121" s="3"/>
-      <c r="R121" s="3">
+      <c r="R121">
         <v>1043.9534356090001</v>
       </c>
     </row>
@@ -20238,38 +19312,31 @@
       <c r="B122" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C122" s="3">
+      <c r="C122">
         <v>3.3030662639999999</v>
       </c>
-      <c r="D122" s="3">
+      <c r="D122">
         <v>138.24119630499999</v>
       </c>
-      <c r="E122" s="3"/>
-      <c r="F122" s="3"/>
-      <c r="G122" s="3">
+      <c r="G122">
         <v>3.7509129720000001</v>
       </c>
-      <c r="H122" s="3">
+      <c r="H122">
         <v>114.541007921</v>
       </c>
-      <c r="I122" s="3"/>
-      <c r="J122" s="3"/>
-      <c r="K122" s="3">
+      <c r="K122">
         <v>4.1248394790000003</v>
       </c>
-      <c r="L122" s="3">
+      <c r="L122">
         <v>402.16483799999997</v>
       </c>
-      <c r="M122" s="3"/>
-      <c r="N122" s="3"/>
-      <c r="O122" s="3">
+      <c r="O122">
         <v>3.765218715</v>
       </c>
-      <c r="P122" s="3">
+      <c r="P122">
         <v>395.38007170899999</v>
       </c>
-      <c r="Q122" s="3"/>
-      <c r="R122" s="3">
+      <c r="R122">
         <v>1065.2711513649999</v>
       </c>
     </row>
@@ -20277,38 +19344,31 @@
       <c r="B123" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C123" s="3">
+      <c r="C123">
         <v>3.686861645</v>
       </c>
-      <c r="D123" s="3">
+      <c r="D123">
         <v>139.04477271100001</v>
       </c>
-      <c r="E123" s="3"/>
-      <c r="F123" s="3"/>
-      <c r="G123" s="3">
+      <c r="G123">
         <v>2.781531003</v>
       </c>
-      <c r="H123" s="3">
+      <c r="H123">
         <v>115.115314723</v>
       </c>
-      <c r="I123" s="3"/>
-      <c r="J123" s="3"/>
-      <c r="K123" s="3">
+      <c r="K123">
         <v>4.5709283840000001</v>
       </c>
-      <c r="L123" s="3">
+      <c r="L123">
         <v>406.43234200000001</v>
       </c>
-      <c r="M123" s="3"/>
-      <c r="N123" s="3"/>
-      <c r="O123" s="3">
+      <c r="O123">
         <v>4.2317483349999998</v>
       </c>
-      <c r="P123" s="3">
+      <c r="P123">
         <v>399.24234003999999</v>
       </c>
-      <c r="Q123" s="3"/>
-      <c r="R123" s="3">
+      <c r="R123">
         <v>1075.1058388410001</v>
       </c>
     </row>
@@ -20316,38 +19376,31 @@
       <c r="B124" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C124" s="3">
+      <c r="C124">
         <v>3.1469548619999999</v>
       </c>
-      <c r="D124" s="3">
+      <c r="D124">
         <v>139.49147205400001</v>
       </c>
-      <c r="E124" s="3"/>
-      <c r="F124" s="3"/>
-      <c r="G124" s="3">
+      <c r="G124">
         <v>2.239807125</v>
       </c>
-      <c r="H124" s="3">
+      <c r="H124">
         <v>115.633221859</v>
       </c>
-      <c r="I124" s="3"/>
-      <c r="J124" s="3"/>
-      <c r="K124" s="3">
+      <c r="K124">
         <v>4.2117921989999996</v>
       </c>
-      <c r="L124" s="3">
+      <c r="L124">
         <v>407.71126800000002</v>
       </c>
-      <c r="M124" s="3"/>
-      <c r="N124" s="3"/>
-      <c r="O124" s="3">
+      <c r="O124">
         <v>3.844524609</v>
       </c>
-      <c r="P124" s="3">
+      <c r="P124">
         <v>400.00910879499997</v>
       </c>
-      <c r="Q124" s="3"/>
-      <c r="R124" s="3">
+      <c r="R124">
         <v>1076.2881495030001</v>
       </c>
     </row>
@@ -20355,38 +19408,31 @@
       <c r="B125" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C125" s="3">
+      <c r="C125">
         <v>2.6086100590000001</v>
       </c>
-      <c r="D125" s="3">
+      <c r="D125">
         <v>139.38144458599999</v>
       </c>
-      <c r="E125" s="3"/>
-      <c r="F125" s="3"/>
-      <c r="G125" s="3">
+      <c r="G125">
         <v>1.8432567959999999</v>
       </c>
-      <c r="H125" s="3">
+      <c r="H125">
         <v>116.058431347</v>
       </c>
-      <c r="I125" s="3"/>
-      <c r="J125" s="3"/>
-      <c r="K125" s="3">
+      <c r="K125">
         <v>3.7203843390000002</v>
       </c>
-      <c r="L125" s="3">
+      <c r="L125">
         <v>408.44207699999998</v>
       </c>
-      <c r="M125" s="3"/>
-      <c r="N125" s="3"/>
-      <c r="O125" s="3">
+      <c r="O125">
         <v>3.3351217019999999</v>
       </c>
-      <c r="P125" s="3">
+      <c r="P125">
         <v>400.16546693700002</v>
       </c>
-      <c r="Q125" s="3"/>
-      <c r="R125" s="3">
+      <c r="R125">
         <v>1075.554792766</v>
       </c>
     </row>
@@ -20394,38 +19440,31 @@
       <c r="B126" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C126" s="3">
+      <c r="C126">
         <v>2.037286565</v>
       </c>
-      <c r="D126" s="3">
+      <c r="D126">
         <v>141.057565625</v>
       </c>
-      <c r="E126" s="3"/>
-      <c r="F126" s="3"/>
-      <c r="G126" s="3">
+      <c r="G126">
         <v>1.6458909370000001</v>
       </c>
-      <c r="H126" s="3">
+      <c r="H126">
         <v>116.42622799</v>
       </c>
-      <c r="I126" s="3"/>
-      <c r="J126" s="3"/>
-      <c r="K126" s="3">
+      <c r="K126">
         <v>3.1953233559999998</v>
       </c>
-      <c r="L126" s="3">
+      <c r="L126">
         <v>415.01530500000001</v>
       </c>
-      <c r="M126" s="3"/>
-      <c r="N126" s="3"/>
-      <c r="O126" s="3">
+      <c r="O126">
         <v>2.7763965530000001</v>
       </c>
-      <c r="P126" s="3">
+      <c r="P126">
         <v>406.35739039100002</v>
       </c>
-      <c r="Q126" s="3"/>
-      <c r="R126" s="3">
+      <c r="R126">
         <v>1088.511386417</v>
       </c>
     </row>
@@ -20433,38 +19472,31 @@
       <c r="B127" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C127" s="3">
+      <c r="C127">
         <v>1.807627756</v>
       </c>
-      <c r="D127" s="3">
+      <c r="D127">
         <v>141.55818461600001</v>
       </c>
-      <c r="E127" s="3"/>
-      <c r="F127" s="3"/>
-      <c r="G127" s="3">
+      <c r="G127">
         <v>1.5730893100000001</v>
       </c>
-      <c r="H127" s="3">
+      <c r="H127">
         <v>116.926181433</v>
       </c>
-      <c r="I127" s="3"/>
-      <c r="J127" s="3"/>
-      <c r="K127" s="3">
+      <c r="K127">
         <v>2.9876288729999998</v>
       </c>
-      <c r="L127" s="3">
+      <c r="L127">
         <v>418.57503200000002</v>
       </c>
-      <c r="M127" s="3"/>
-      <c r="N127" s="3"/>
-      <c r="O127" s="3">
+      <c r="O127">
         <v>2.565283413</v>
       </c>
-      <c r="P127" s="3">
+      <c r="P127">
         <v>409.48403756800002</v>
       </c>
-      <c r="Q127" s="3"/>
-      <c r="R127" s="3">
+      <c r="R127">
         <v>1095.4770649689999</v>
       </c>
     </row>
@@ -20472,38 +19504,31 @@
       <c r="B128" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C128" s="3">
+      <c r="C128">
         <v>1.897723807</v>
       </c>
-      <c r="D128" s="3">
+      <c r="D128">
         <v>142.13863492799999</v>
       </c>
-      <c r="E128" s="3"/>
-      <c r="F128" s="3"/>
-      <c r="G128" s="3">
+      <c r="G128">
         <v>1.627901732</v>
       </c>
-      <c r="H128" s="3">
+      <c r="H128">
         <v>117.515617081</v>
       </c>
-      <c r="I128" s="3"/>
-      <c r="J128" s="3"/>
-      <c r="K128" s="3">
+      <c r="K128">
         <v>3.0447524939999999</v>
       </c>
-      <c r="L128" s="3">
+      <c r="L128">
         <v>420.125067</v>
       </c>
-      <c r="M128" s="3"/>
-      <c r="N128" s="3"/>
-      <c r="O128" s="3">
+      <c r="O128">
         <v>2.6589640540000001</v>
       </c>
-      <c r="P128" s="3">
+      <c r="P128">
         <v>410.645207212</v>
       </c>
-      <c r="Q128" s="3"/>
-      <c r="R128" s="3">
+      <c r="R128">
         <v>1099.653868308</v>
       </c>
     </row>
@@ -20511,38 +19536,31 @@
       <c r="B129" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C129" s="3">
+      <c r="C129">
         <v>1.9720394919999999</v>
       </c>
-      <c r="D129" s="3">
+      <c r="D129">
         <v>142.13010171799999</v>
       </c>
-      <c r="E129" s="3"/>
-      <c r="F129" s="3"/>
-      <c r="G129" s="3">
+      <c r="G129">
         <v>1.7775703970000001</v>
       </c>
-      <c r="H129" s="3">
+      <c r="H129">
         <v>118.121451666</v>
       </c>
-      <c r="I129" s="3"/>
-      <c r="J129" s="3"/>
-      <c r="K129" s="3">
+      <c r="K129">
         <v>3.0746296000000002</v>
       </c>
-      <c r="L129" s="3">
+      <c r="L129">
         <v>421.000158</v>
       </c>
-      <c r="M129" s="3"/>
-      <c r="N129" s="3"/>
-      <c r="O129" s="3">
+      <c r="O129">
         <v>2.7363765930000001</v>
       </c>
-      <c r="P129" s="3">
+      <c r="P129">
         <v>411.115501107</v>
       </c>
-      <c r="Q129" s="3"/>
-      <c r="R129" s="3">
+      <c r="R129">
         <v>1101.9278285730002</v>
       </c>
     </row>
@@ -20550,38 +19568,31 @@
       <c r="B130" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C130" s="3">
+      <c r="C130">
         <v>1.9839849110000001</v>
       </c>
-      <c r="D130" s="3">
+      <c r="D130">
         <v>143.85612644299999</v>
       </c>
-      <c r="E130" s="3"/>
-      <c r="F130" s="3"/>
-      <c r="G130" s="3">
+      <c r="G130">
         <v>1.9907433269999999</v>
       </c>
-      <c r="H130" s="3">
+      <c r="H130">
         <v>118.743975354</v>
       </c>
-      <c r="I130" s="3"/>
-      <c r="J130" s="3"/>
-      <c r="K130" s="3">
+      <c r="K130">
         <v>3.0615355260000001</v>
       </c>
-      <c r="L130" s="3">
+      <c r="L130">
         <v>427.72114599999998</v>
       </c>
-      <c r="M130" s="3"/>
-      <c r="N130" s="3"/>
-      <c r="O130" s="3">
+      <c r="O130">
         <v>2.7499675039999998</v>
       </c>
-      <c r="P130" s="3">
+      <c r="P130">
         <v>417.53208657699997</v>
       </c>
-      <c r="Q130" s="3"/>
-      <c r="R130" s="3">
+      <c r="R130">
         <v>1117.639565642</v>
       </c>
     </row>
@@ -20589,38 +19600,31 @@
       <c r="B131" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C131" s="3">
+      <c r="C131">
         <v>2</v>
       </c>
-      <c r="D131" s="3">
+      <c r="D131">
         <v>144.389348308</v>
       </c>
-      <c r="E131" s="3"/>
-      <c r="F131" s="3"/>
-      <c r="G131" s="3">
+      <c r="G131">
         <v>2.0710625139999999</v>
       </c>
-      <c r="H131" s="3">
+      <c r="H131">
         <v>119.34779574700001</v>
       </c>
-      <c r="I131" s="3"/>
-      <c r="J131" s="3"/>
-      <c r="K131" s="3">
+      <c r="K131">
         <v>3.0332157990000002</v>
       </c>
-      <c r="L131" s="3">
+      <c r="L131">
         <v>431.27131600000001</v>
       </c>
-      <c r="M131" s="3"/>
-      <c r="N131" s="3"/>
-      <c r="O131" s="3">
+      <c r="O131">
         <v>2.7671967209999999</v>
       </c>
-      <c r="P131" s="3">
+      <c r="P131">
         <v>420.81526642799997</v>
       </c>
-      <c r="Q131" s="3"/>
-      <c r="R131" s="3">
+      <c r="R131">
         <v>1125.695201517</v>
       </c>
     </row>
@@ -20628,38 +19632,31 @@
       <c r="B132" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C132" s="3">
+      <c r="C132">
         <v>2</v>
       </c>
-      <c r="D132" s="3">
+      <c r="D132">
         <v>144.98140762700001</v>
       </c>
-      <c r="E132" s="3"/>
-      <c r="F132" s="3"/>
-      <c r="G132" s="3">
+      <c r="G132">
         <v>2.0602177049999999</v>
       </c>
-      <c r="H132" s="3">
+      <c r="H132">
         <v>119.93669463000001</v>
       </c>
-      <c r="I132" s="3"/>
-      <c r="J132" s="3"/>
-      <c r="K132" s="3">
+      <c r="K132">
         <v>2.9724379669999998</v>
       </c>
-      <c r="L132" s="3">
+      <c r="L132">
         <v>432.613024</v>
       </c>
-      <c r="M132" s="3"/>
-      <c r="N132" s="3"/>
-      <c r="O132" s="3">
+      <c r="O132">
         <v>2.7655999549999999</v>
       </c>
-      <c r="P132" s="3">
+      <c r="P132">
         <v>422.00201087699998</v>
       </c>
-      <c r="Q132" s="3"/>
-      <c r="R132" s="3">
+      <c r="R132">
         <v>1129.331392761</v>
       </c>
     </row>
@@ -20667,38 +19664,31 @@
       <c r="B133" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C133" s="3">
+      <c r="C133">
         <v>2</v>
       </c>
-      <c r="D133" s="3">
+      <c r="D133">
         <v>144.972703752</v>
       </c>
-      <c r="E133" s="3"/>
-      <c r="F133" s="3"/>
-      <c r="G133" s="3">
+      <c r="G133">
         <v>2.0253607250000001</v>
       </c>
-      <c r="H133" s="3">
+      <c r="H133">
         <v>120.51383715599999</v>
       </c>
-      <c r="I133" s="3"/>
-      <c r="J133" s="3"/>
-      <c r="K133" s="3">
+      <c r="K133">
         <v>2.922492965</v>
       </c>
-      <c r="L133" s="3">
+      <c r="L133">
         <v>433.30385799999999</v>
       </c>
-      <c r="M133" s="3"/>
-      <c r="N133" s="3"/>
-      <c r="O133" s="3">
+      <c r="O133">
         <v>2.7652007240000001</v>
       </c>
-      <c r="P133" s="3">
+      <c r="P133">
         <v>422.48366991799998</v>
       </c>
-      <c r="Q133" s="3"/>
-      <c r="R133" s="3">
+      <c r="R133">
         <v>1130.9871232399998</v>
       </c>
     </row>
@@ -20706,38 +19696,31 @@
       <c r="B134" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C134" s="3">
+      <c r="C134">
         <v>2.0006912909999999</v>
       </c>
-      <c r="D134" s="3">
+      <c r="D134">
         <v>146.73424343600001</v>
       </c>
-      <c r="E134" s="3"/>
-      <c r="F134" s="3"/>
-      <c r="G134" s="3">
+      <c r="G134">
         <v>1.983014214</v>
       </c>
-      <c r="H134" s="3">
+      <c r="H134">
         <v>121.098685264</v>
       </c>
-      <c r="I134" s="3"/>
-      <c r="J134" s="3"/>
-      <c r="K134" s="3">
+      <c r="K134">
         <v>2.8511103819999999</v>
       </c>
-      <c r="L134" s="3">
+      <c r="L134">
         <v>439.91594800000001</v>
       </c>
-      <c r="M134" s="3"/>
-      <c r="N134" s="3"/>
-      <c r="O134" s="3">
+      <c r="O134">
         <v>2.7624298029999999</v>
       </c>
-      <c r="P134" s="3">
+      <c r="P134">
         <v>429.06611737499998</v>
       </c>
-      <c r="Q134" s="3"/>
-      <c r="R134" s="3">
+      <c r="R134">
         <v>1146.4122397650001</v>
       </c>
     </row>
@@ -20745,38 +19728,31 @@
       <c r="B135" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C135" s="3">
+      <c r="C135">
         <v>2.000225854</v>
       </c>
-      <c r="D135" s="3">
+      <c r="D135">
         <v>147.277461383</v>
       </c>
-      <c r="E135" s="3"/>
-      <c r="F135" s="3"/>
-      <c r="G135" s="3">
+      <c r="G135">
         <v>1.954338439</v>
       </c>
-      <c r="H135" s="3">
+      <c r="H135">
         <v>121.68025559500001</v>
       </c>
-      <c r="I135" s="3"/>
-      <c r="J135" s="3"/>
-      <c r="K135" s="3">
+      <c r="K135">
         <v>2.8186613739999999</v>
       </c>
-      <c r="L135" s="3">
+      <c r="L135">
         <v>443.42739399999999</v>
       </c>
-      <c r="M135" s="3"/>
-      <c r="N135" s="3"/>
-      <c r="O135" s="3">
+      <c r="O135">
         <v>2.7589968790000001</v>
       </c>
-      <c r="P135" s="3">
+      <c r="P135">
         <v>432.42554649499999</v>
       </c>
-      <c r="Q135" s="3"/>
-      <c r="R135" s="3">
+      <c r="R135">
         <v>1154.3428800189999</v>
       </c>
     </row>
@@ -20784,38 +19760,31 @@
       <c r="B136" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C136" s="3">
+      <c r="C136">
         <v>2.0007676779999999</v>
       </c>
-      <c r="D136" s="3">
+      <c r="D136">
         <v>147.88214876999999</v>
       </c>
-      <c r="E136" s="3"/>
-      <c r="F136" s="3"/>
-      <c r="G136" s="3">
+      <c r="G136">
         <v>1.934911058</v>
       </c>
-      <c r="H136" s="3">
+      <c r="H136">
         <v>122.257362997</v>
       </c>
-      <c r="I136" s="3"/>
-      <c r="J136" s="3"/>
-      <c r="K136" s="3">
+      <c r="K136">
         <v>2.8127976559999999</v>
       </c>
-      <c r="L136" s="3">
+      <c r="L136">
         <v>444.78155299999997</v>
       </c>
-      <c r="M136" s="3"/>
-      <c r="N136" s="3"/>
-      <c r="O136" s="3">
+      <c r="O136">
         <v>2.7567236359999998</v>
       </c>
-      <c r="P136" s="3">
+      <c r="P136">
         <v>433.63544005400001</v>
       </c>
-      <c r="Q136" s="3"/>
-      <c r="R136" s="3">
+      <c r="R136">
         <v>1158.0617048489999</v>
       </c>
     </row>
@@ -20823,38 +19792,31 @@
       <c r="B137" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C137" s="3">
+      <c r="C137">
         <v>1.999924531</v>
       </c>
-      <c r="D137" s="3">
+      <c r="D137">
         <v>147.87204841799999</v>
       </c>
-      <c r="E137" s="3"/>
-      <c r="F137" s="3"/>
-      <c r="G137" s="3">
+      <c r="G137">
         <v>1.917169278</v>
       </c>
-      <c r="H137" s="3">
+      <c r="H137">
         <v>122.824291417</v>
       </c>
-      <c r="I137" s="3"/>
-      <c r="J137" s="3"/>
-      <c r="K137" s="3">
+      <c r="K137">
         <v>2.8205246210000001</v>
       </c>
-      <c r="L137" s="3">
+      <c r="L137">
         <v>445.52530000000002</v>
       </c>
-      <c r="M137" s="3"/>
-      <c r="N137" s="3"/>
-      <c r="O137" s="3">
+      <c r="O137">
         <v>2.755375892</v>
       </c>
-      <c r="P137" s="3">
+      <c r="P137">
         <v>434.12468310499997</v>
       </c>
-      <c r="Q137" s="3"/>
-      <c r="R137" s="3">
+      <c r="R137">
         <v>1159.8393172619999</v>
       </c>
     </row>
@@ -20862,38 +19824,31 @@
       <c r="B138" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C138" s="3">
+      <c r="C138">
         <v>1.999900233</v>
       </c>
-      <c r="D138" s="3">
+      <c r="D138">
         <v>149.668781913</v>
       </c>
-      <c r="E138" s="3"/>
-      <c r="F138" s="3"/>
-      <c r="G138" s="3">
+      <c r="G138">
         <v>1.890523202</v>
       </c>
-      <c r="H138" s="3">
+      <c r="H138">
         <v>123.388084005</v>
       </c>
-      <c r="I138" s="3"/>
-      <c r="J138" s="3"/>
-      <c r="K138" s="3">
+      <c r="K138">
         <v>2.8371817519999998</v>
       </c>
-      <c r="L138" s="3">
+      <c r="L138">
         <v>452.39716299999998</v>
       </c>
-      <c r="M138" s="3"/>
-      <c r="N138" s="3"/>
-      <c r="O138" s="3">
+      <c r="O138">
         <v>2.756173215</v>
       </c>
-      <c r="P138" s="3">
+      <c r="P138">
         <v>440.89192277900003</v>
       </c>
-      <c r="Q138" s="3"/>
-      <c r="R138" s="3">
+      <c r="R138">
         <v>1175.829730099</v>
       </c>
     </row>
@@ -20901,38 +19856,31 @@
       <c r="B139" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C139" s="3">
+      <c r="C139">
         <v>2.000222569</v>
       </c>
-      <c r="D139" s="3">
+      <c r="D139">
         <v>150.22333840499999</v>
       </c>
-      <c r="E139" s="3"/>
-      <c r="F139" s="3"/>
-      <c r="G139" s="3">
+      <c r="G139">
         <v>1.880443533</v>
       </c>
-      <c r="H139" s="3">
+      <c r="H139">
         <v>123.96838409199999</v>
       </c>
-      <c r="I139" s="3"/>
-      <c r="J139" s="3"/>
-      <c r="K139" s="3">
+      <c r="K139">
         <v>2.8361515709999998</v>
       </c>
-      <c r="L139" s="3">
+      <c r="L139">
         <v>456.00366700000001</v>
       </c>
-      <c r="M139" s="3"/>
-      <c r="N139" s="3"/>
-      <c r="O139" s="3">
+      <c r="O139">
         <v>2.7571039289999999</v>
       </c>
-      <c r="P139" s="3">
+      <c r="P139">
         <v>444.34796822999999</v>
       </c>
-      <c r="Q139" s="3"/>
-      <c r="R139" s="3">
+      <c r="R139">
         <v>1184.0172793289998</v>
       </c>
     </row>
@@ -20940,38 +19888,31 @@
       <c r="B140" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C140" s="3">
+      <c r="C140">
         <v>1.999630088</v>
       </c>
-      <c r="D140" s="3">
+      <c r="D140">
         <v>150.83924471099999</v>
       </c>
-      <c r="E140" s="3"/>
-      <c r="F140" s="3"/>
-      <c r="G140" s="3">
+      <c r="G140">
         <v>1.8767782099999999</v>
       </c>
-      <c r="H140" s="3">
+      <c r="H140">
         <v>124.55186254500001</v>
       </c>
-      <c r="I140" s="3"/>
-      <c r="J140" s="3"/>
-      <c r="K140" s="3">
+      <c r="K140">
         <v>2.850527391</v>
       </c>
-      <c r="L140" s="3">
+      <c r="L140">
         <v>457.460173</v>
       </c>
-      <c r="M140" s="3"/>
-      <c r="N140" s="3"/>
-      <c r="O140" s="3">
+      <c r="O140">
         <v>2.755942653</v>
       </c>
-      <c r="P140" s="3">
+      <c r="P140">
         <v>445.58618410600002</v>
       </c>
-      <c r="Q140" s="3"/>
-      <c r="R140" s="3">
+      <c r="R140">
         <v>1187.9203427040002</v>
       </c>
     </row>
@@ -20979,38 +19920,31 @@
       <c r="B141" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C141" s="3">
+      <c r="C141">
         <v>1.9993326199999999</v>
       </c>
-      <c r="D141" s="3">
+      <c r="D141">
         <v>150.828502517</v>
       </c>
-      <c r="E141" s="3"/>
-      <c r="F141" s="3"/>
-      <c r="G141" s="3">
+      <c r="G141">
         <v>1.8767859170000001</v>
       </c>
-      <c r="H141" s="3">
+      <c r="H141">
         <v>125.129440422</v>
       </c>
-      <c r="I141" s="3"/>
-      <c r="J141" s="3"/>
-      <c r="K141" s="3">
+      <c r="K141">
         <v>2.7805866469999998</v>
       </c>
-      <c r="L141" s="3">
+      <c r="L141">
         <v>457.91351700000001</v>
       </c>
-      <c r="M141" s="3"/>
-      <c r="N141" s="3"/>
-      <c r="O141" s="3">
+      <c r="O141">
         <v>2.6841176080000002</v>
       </c>
-      <c r="P141" s="3">
+      <c r="P141">
         <v>445.77710016700001</v>
       </c>
-      <c r="Q141" s="3"/>
-      <c r="R141" s="3">
+      <c r="R141">
         <v>1188.989382898</v>
       </c>
     </row>
@@ -21018,52 +19952,52 @@
       <c r="B142" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C142" s="3">
+      <c r="C142">
         <v>49.622322332000003</v>
       </c>
-      <c r="D142" s="3">
+      <c r="D142">
         <v>3163.6423567420002</v>
       </c>
-      <c r="E142" s="3">
+      <c r="E142">
         <v>271.35878983800018</v>
       </c>
-      <c r="F142" s="3">
+      <c r="F142">
         <v>10670.371999998997</v>
       </c>
-      <c r="G142" s="3">
+      <c r="G142">
         <v>49.013283054999995</v>
       </c>
-      <c r="H142" s="3">
+      <c r="H142">
         <v>2620.836017952</v>
       </c>
-      <c r="I142" s="3">
+      <c r="I142">
         <v>134.24133987499997</v>
       </c>
-      <c r="J142" s="3">
+      <c r="J142">
         <v>4749.3</v>
       </c>
-      <c r="K142" s="3">
+      <c r="K142">
         <v>70.467117497000004</v>
       </c>
-      <c r="L142" s="3">
+      <c r="L142">
         <v>16676.821753000004</v>
       </c>
-      <c r="M142" s="3">
+      <c r="M142">
         <v>387.65680250600008</v>
       </c>
-      <c r="N142" s="3">
+      <c r="N142">
         <v>32928.059998000004</v>
       </c>
-      <c r="O142" s="3">
+      <c r="O142">
         <v>64.852675906000002</v>
       </c>
-      <c r="P142" s="3">
+      <c r="P142">
         <v>9193.5373213000003</v>
       </c>
-      <c r="Q142" s="3">
+      <c r="Q142">
         <v>375.97290989900011</v>
       </c>
-      <c r="R142" s="3">
+      <c r="R142">
         <v>81405.754687901004</v>
       </c>
     </row>
@@ -21074,10 +20008,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CBCFF9D-2AF3-4828-982D-3B16181A01C3}">
-  <dimension ref="B3:Q142"/>
+  <dimension ref="B3:T142"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="20" max="20" width="10.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>158</v>
       </c>
@@ -21085,98 +20022,134 @@
         <v>155</v>
       </c>
     </row>
-    <row r="4" spans="2:17" s="4" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="2:20" s="3" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="2:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>140</v>
       </c>
       <c r="F5">
         <v>68.099999999999994</v>
       </c>
-    </row>
-    <row r="6" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="I5" s="5">
+        <f>[1]data!$B$56</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J5" s="5">
+        <f t="shared" ref="J5:J61" si="0">J9*(1-I9/100)</f>
+        <v>58.198347376024309</v>
+      </c>
+      <c r="T5" s="4"/>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>141</v>
       </c>
       <c r="F6">
         <v>68.900000000000006</v>
       </c>
+      <c r="I6" s="5">
+        <f>I5</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J6" s="5">
+        <f t="shared" si="0"/>
+        <v>58.271277635893995</v>
+      </c>
       <c r="N6">
         <v>216.7</v>
       </c>
-    </row>
-    <row r="7" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T6" s="4"/>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>142</v>
       </c>
       <c r="F7">
         <v>68.900000000000006</v>
       </c>
+      <c r="I7" s="5">
+        <f>I6</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J7" s="5">
+        <f t="shared" si="0"/>
+        <v>58.562998675372832</v>
+      </c>
       <c r="N7">
         <v>227.63</v>
       </c>
-    </row>
-    <row r="8" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T7" s="4"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>143</v>
       </c>
       <c r="F8">
         <v>69.400000000000006</v>
       </c>
+      <c r="I8" s="5">
+        <f>I7</f>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="J8" s="5">
+        <f t="shared" si="0"/>
+        <v>58.927649974721355</v>
+      </c>
       <c r="N8">
         <v>229.86</v>
       </c>
-    </row>
-    <row r="9" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T8" s="4"/>
+    </row>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>28</v>
       </c>
@@ -21186,14 +20159,23 @@
       <c r="F9">
         <v>69.400000000000006</v>
       </c>
+      <c r="I9" s="5">
+        <f>[1]data!$B$57</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <f t="shared" si="0"/>
+        <v>58.198347376024309</v>
+      </c>
       <c r="N9">
         <v>241.65</v>
       </c>
       <c r="Q9">
         <v>2.8647568290000001</v>
       </c>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T9" s="4"/>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>29</v>
       </c>
@@ -21203,6 +20185,14 @@
       <c r="F10">
         <v>70</v>
       </c>
+      <c r="I10" s="5">
+        <f>[1]data!$B$57</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <f t="shared" si="0"/>
+        <v>58.271277635893995</v>
+      </c>
       <c r="M10">
         <v>4.2316566680000003</v>
       </c>
@@ -21212,8 +20202,9 @@
       <c r="Q10">
         <v>2.5590551179999999</v>
       </c>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T10" s="4"/>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>30</v>
       </c>
@@ -21223,6 +20214,14 @@
       <c r="F11">
         <v>70.3</v>
       </c>
+      <c r="I11" s="5">
+        <f>[1]data!$B$57</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <f t="shared" si="0"/>
+        <v>58.562998675372832</v>
+      </c>
       <c r="M11">
         <v>0.38659227699999998</v>
       </c>
@@ -21232,8 +20231,9 @@
       <c r="Q11">
         <v>2.8141361260000002</v>
       </c>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T11" s="4"/>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>31</v>
       </c>
@@ -21243,6 +20243,14 @@
       <c r="F12">
         <v>70.599999999999994</v>
       </c>
+      <c r="I12" s="5">
+        <f>[1]data!$B$57</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <f t="shared" si="0"/>
+        <v>58.927649974721355</v>
+      </c>
       <c r="M12">
         <v>2.3579570169999999</v>
       </c>
@@ -21252,8 +20260,9 @@
       <c r="Q12">
         <v>2.7958387519999999</v>
       </c>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T12" s="4"/>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>32</v>
       </c>
@@ -21263,6 +20272,14 @@
       <c r="F13">
         <v>70.5</v>
       </c>
+      <c r="I13" s="5">
+        <f>[1]data!$B$58</f>
+        <v>1.3</v>
+      </c>
+      <c r="J13" s="5">
+        <f t="shared" si="0"/>
+        <v>58.964890958484609</v>
+      </c>
       <c r="M13">
         <v>-0.87316366599999995</v>
       </c>
@@ -21272,8 +20289,9 @@
       <c r="Q13">
         <v>2.5906735749999998</v>
       </c>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T13" s="4"/>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>33</v>
       </c>
@@ -21283,6 +20301,14 @@
       <c r="F14">
         <v>71.3</v>
       </c>
+      <c r="I14" s="5">
+        <f>[1]data!$B$58</f>
+        <v>1.3</v>
+      </c>
+      <c r="J14" s="5">
+        <f t="shared" si="0"/>
+        <v>59.038781799284699</v>
+      </c>
       <c r="M14">
         <v>14.769557710000001</v>
       </c>
@@ -21292,8 +20318,9 @@
       <c r="Q14">
         <v>2.9430582209999998</v>
       </c>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T14" s="4"/>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>34</v>
       </c>
@@ -21303,6 +20330,14 @@
       <c r="F15">
         <v>71.2</v>
       </c>
+      <c r="I15" s="5">
+        <f>[1]data!$B$58</f>
+        <v>1.3</v>
+      </c>
+      <c r="J15" s="5">
+        <f t="shared" si="0"/>
+        <v>59.334345162485143</v>
+      </c>
       <c r="M15">
         <v>19.911601243</v>
       </c>
@@ -21312,8 +20347,9 @@
       <c r="Q15">
         <v>2.5461489500000001</v>
       </c>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T15" s="4"/>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>35</v>
       </c>
@@ -21323,6 +20359,14 @@
       <c r="F16">
         <v>71.599999999999994</v>
       </c>
+      <c r="I16" s="5">
+        <f>[1]data!$B$58</f>
+        <v>1.3</v>
+      </c>
+      <c r="J16" s="5">
+        <f t="shared" si="0"/>
+        <v>59.703799366485669</v>
+      </c>
       <c r="M16">
         <v>25.055253315000002</v>
       </c>
@@ -21332,8 +20376,9 @@
       <c r="Q16">
         <v>2.5300442759999999</v>
       </c>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T16" s="4"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>36</v>
       </c>
@@ -21343,6 +20388,14 @@
       <c r="F17">
         <v>71.599999999999994</v>
       </c>
+      <c r="I17" s="5">
+        <f>[1]data!$B$59</f>
+        <v>1.4</v>
+      </c>
+      <c r="J17" s="5">
+        <f t="shared" si="0"/>
+        <v>59.802120647550318</v>
+      </c>
       <c r="M17">
         <v>29.853051682</v>
       </c>
@@ -21352,8 +20405,9 @@
       <c r="Q17">
         <v>2.525252525</v>
       </c>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T17" s="4"/>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>37</v>
       </c>
@@ -21363,6 +20417,14 @@
       <c r="F18">
         <v>72.3</v>
       </c>
+      <c r="I18" s="5">
+        <f>[1]data!$B$59</f>
+        <v>1.4</v>
+      </c>
+      <c r="J18" s="5">
+        <f t="shared" si="0"/>
+        <v>59.877060648361763</v>
+      </c>
       <c r="M18">
         <v>20.113412798999999</v>
       </c>
@@ -21372,8 +20434,9 @@
       <c r="Q18">
         <v>2.2995649469999999</v>
       </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T18" s="4"/>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>38</v>
       </c>
@@ -21383,6 +20446,14 @@
       <c r="F19">
         <v>72.099999999999994</v>
       </c>
+      <c r="I19" s="5">
+        <f>[1]data!$B$59</f>
+        <v>1.4</v>
+      </c>
+      <c r="J19" s="5">
+        <f t="shared" si="0"/>
+        <v>60.176820651607649</v>
+      </c>
       <c r="M19">
         <v>11.043392577000001</v>
       </c>
@@ -21392,8 +20463,9 @@
       <c r="Q19">
         <v>2.172563625</v>
       </c>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T19" s="4"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>39</v>
       </c>
@@ -21403,6 +20475,14 @@
       <c r="F20">
         <v>72.5</v>
       </c>
+      <c r="I20" s="5">
+        <f>[1]data!$B$59</f>
+        <v>1.4</v>
+      </c>
+      <c r="J20" s="5">
+        <f t="shared" si="0"/>
+        <v>60.55152065566498</v>
+      </c>
       <c r="M20">
         <v>0.710328654</v>
       </c>
@@ -21412,8 +20492,9 @@
       <c r="Q20">
         <v>2.1591610120000002</v>
       </c>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T20" s="4"/>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>40</v>
       </c>
@@ -21423,6 +20504,14 @@
       <c r="F21">
         <v>72.099999999999994</v>
       </c>
+      <c r="I21" s="5">
+        <f>[1]data!$B$60</f>
+        <v>1</v>
+      </c>
+      <c r="J21" s="5">
+        <f t="shared" si="0"/>
+        <v>60.406182472273052</v>
+      </c>
       <c r="M21">
         <v>-7.5357659540000004</v>
       </c>
@@ -21432,8 +20521,9 @@
       <c r="Q21">
         <v>2.0935960589999998</v>
       </c>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T21" s="4"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>41</v>
       </c>
@@ -21443,6 +20533,14 @@
       <c r="F22">
         <v>72.7</v>
       </c>
+      <c r="I22" s="5">
+        <f>[1]data!$B$60</f>
+        <v>1</v>
+      </c>
+      <c r="J22" s="5">
+        <f t="shared" si="0"/>
+        <v>60.481879442789662</v>
+      </c>
       <c r="M22">
         <v>-2.3348427919999999</v>
       </c>
@@ -21452,8 +20550,9 @@
       <c r="Q22">
         <v>2.0656136090000001</v>
       </c>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T22" s="4"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>42</v>
       </c>
@@ -21463,6 +20562,14 @@
       <c r="F23">
         <v>72.7</v>
       </c>
+      <c r="I23" s="5">
+        <f>[1]data!$B$60</f>
+        <v>1</v>
+      </c>
+      <c r="J23" s="5">
+        <f t="shared" si="0"/>
+        <v>60.784667324856208</v>
+      </c>
       <c r="M23">
         <v>3.503467315</v>
       </c>
@@ -21472,8 +20579,9 @@
       <c r="Q23">
         <v>2.12636695</v>
       </c>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T23" s="4"/>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>43</v>
       </c>
@@ -21483,6 +20591,14 @@
       <c r="F24">
         <v>73.2</v>
       </c>
+      <c r="I24" s="5">
+        <f>[1]data!$B$60</f>
+        <v>1</v>
+      </c>
+      <c r="J24" s="5">
+        <f t="shared" si="0"/>
+        <v>61.163152177439372</v>
+      </c>
       <c r="M24">
         <v>7.7652537800000001</v>
       </c>
@@ -21492,8 +20608,9 @@
       <c r="Q24">
         <v>2.1135265699999999</v>
       </c>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T24" s="4"/>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>44</v>
       </c>
@@ -21503,6 +20620,14 @@
       <c r="F25">
         <v>72.8</v>
       </c>
+      <c r="I25" s="5">
+        <f>[1]data!$B$61</f>
+        <v>1.7</v>
+      </c>
+      <c r="J25" s="5">
+        <f t="shared" si="0"/>
+        <v>61.450846869046849</v>
+      </c>
       <c r="M25">
         <v>34.616320711999997</v>
       </c>
@@ -21512,8 +20637,9 @@
       <c r="Q25">
         <v>1.869722557</v>
       </c>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T25" s="4"/>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>45</v>
       </c>
@@ -21523,6 +20649,14 @@
       <c r="F26">
         <v>73.8</v>
       </c>
+      <c r="I26" s="5">
+        <f>[1]data!$B$61</f>
+        <v>1.7</v>
+      </c>
+      <c r="J26" s="5">
+        <f t="shared" si="0"/>
+        <v>61.52785294281756</v>
+      </c>
       <c r="M26">
         <v>-13.04505097</v>
       </c>
@@ -21532,8 +20666,9 @@
       <c r="Q26">
         <v>2.2619047619999999</v>
       </c>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T26" s="4"/>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>46</v>
       </c>
@@ -21543,6 +20678,14 @@
       <c r="F27">
         <v>73.8</v>
       </c>
+      <c r="I27" s="5">
+        <f>[1]data!$B$61</f>
+        <v>1.7</v>
+      </c>
+      <c r="J27" s="5">
+        <f t="shared" si="0"/>
+        <v>61.835877237900519</v>
+      </c>
       <c r="M27">
         <v>-7.87794113</v>
       </c>
@@ -21552,8 +20695,9 @@
       <c r="Q27">
         <v>2.3795359899999999</v>
       </c>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T27" s="4"/>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>47</v>
       </c>
@@ -21563,6 +20707,14 @@
       <c r="F28">
         <v>73.900000000000006</v>
       </c>
+      <c r="I28" s="5">
+        <f>[1]data!$B$61</f>
+        <v>1.7</v>
+      </c>
+      <c r="J28" s="5">
+        <f t="shared" si="0"/>
+        <v>62.220907606754196</v>
+      </c>
       <c r="M28">
         <v>-8.9468574830000005</v>
       </c>
@@ -21572,8 +20724,9 @@
       <c r="Q28">
         <v>1.9515079829999999</v>
       </c>
-    </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T28" s="4"/>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>48</v>
       </c>
@@ -21583,6 +20736,14 @@
       <c r="F29">
         <v>73.900000000000006</v>
       </c>
+      <c r="I29" s="5">
+        <f>[1]data!$B$62</f>
+        <v>2.1</v>
+      </c>
+      <c r="J29" s="5">
+        <f t="shared" si="0"/>
+        <v>62.768995780436008</v>
+      </c>
       <c r="M29">
         <v>-20.701500632999998</v>
       </c>
@@ -21592,8 +20753,9 @@
       <c r="Q29">
         <v>2.368265246</v>
       </c>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T29" s="4"/>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>49</v>
       </c>
@@ -21603,6 +20765,14 @@
       <c r="F30">
         <v>74.5</v>
       </c>
+      <c r="I30" s="5">
+        <f>[1]data!$B$62</f>
+        <v>2.1</v>
+      </c>
+      <c r="J30" s="5">
+        <f t="shared" si="0"/>
+        <v>62.847653669885148</v>
+      </c>
       <c r="M30">
         <v>16.650909503000001</v>
       </c>
@@ -21612,8 +20782,9 @@
       <c r="Q30">
         <v>1.862630966</v>
       </c>
-    </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T30" s="4"/>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>50</v>
       </c>
@@ -21623,6 +20794,14 @@
       <c r="F31">
         <v>74.599999999999994</v>
       </c>
+      <c r="I31" s="5">
+        <f>[1]data!$B$62</f>
+        <v>2.1</v>
+      </c>
+      <c r="J31" s="5">
+        <f t="shared" si="0"/>
+        <v>63.162285227681842</v>
+      </c>
       <c r="M31">
         <v>5.7769198949999998</v>
       </c>
@@ -21632,8 +20811,9 @@
       <c r="Q31">
         <v>1.9755955839999999</v>
       </c>
-    </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T31" s="4"/>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>51</v>
       </c>
@@ -21643,6 +20823,14 @@
       <c r="F32">
         <v>75</v>
       </c>
+      <c r="I32" s="5">
+        <f>[1]data!$B$62</f>
+        <v>2.1</v>
+      </c>
+      <c r="J32" s="5">
+        <f t="shared" si="0"/>
+        <v>63.555574674927676</v>
+      </c>
       <c r="M32">
         <v>3.5252441879999998</v>
       </c>
@@ -21652,8 +20840,9 @@
       <c r="Q32">
         <v>2.6102088170000002</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T32" s="4"/>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>52</v>
       </c>
@@ -21663,6 +20852,14 @@
       <c r="F33">
         <v>75</v>
       </c>
+      <c r="I33" s="5">
+        <f>[1]data!$B$63</f>
+        <v>2.4</v>
+      </c>
+      <c r="J33" s="5">
+        <f t="shared" si="0"/>
+        <v>64.312495676676235</v>
+      </c>
       <c r="M33">
         <v>-5.1788157119999996</v>
       </c>
@@ -21672,8 +20869,9 @@
       <c r="Q33">
         <v>2.8918449970000002</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T33" s="4"/>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>53</v>
       </c>
@@ -21683,6 +20881,14 @@
       <c r="F34">
         <v>75.5</v>
       </c>
+      <c r="I34" s="5">
+        <f>[1]data!$B$63</f>
+        <v>2.4</v>
+      </c>
+      <c r="J34" s="5">
+        <f t="shared" si="0"/>
+        <v>64.393087776521668</v>
+      </c>
       <c r="M34">
         <v>-2.697270311</v>
       </c>
@@ -21692,8 +20898,9 @@
       <c r="Q34">
         <v>2.914285714</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T34" s="4"/>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>54</v>
       </c>
@@ -21703,6 +20910,14 @@
       <c r="F35">
         <v>75.599999999999994</v>
       </c>
+      <c r="I35" s="5">
+        <f>[1]data!$B$63</f>
+        <v>2.4</v>
+      </c>
+      <c r="J35" s="5">
+        <f t="shared" si="0"/>
+        <v>64.715456175903526</v>
+      </c>
       <c r="M35">
         <v>-2.538451512</v>
       </c>
@@ -21712,8 +20927,9 @@
       <c r="Q35">
         <v>2.8490028490000001</v>
       </c>
-    </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T35" s="4"/>
+    </row>
+    <row r="36" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>55</v>
       </c>
@@ -21723,6 +20939,14 @@
       <c r="F36">
         <v>76</v>
       </c>
+      <c r="I36" s="5">
+        <f>[1]data!$B$63</f>
+        <v>2.4</v>
+      </c>
+      <c r="J36" s="5">
+        <f t="shared" si="0"/>
+        <v>65.118416675130817</v>
+      </c>
       <c r="M36">
         <v>-0.647819009</v>
       </c>
@@ -21732,8 +20956,9 @@
       <c r="Q36">
         <v>2.6003391749999998</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T36" s="4"/>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>56</v>
       </c>
@@ -21743,6 +20968,14 @@
       <c r="F37">
         <v>75.900000000000006</v>
       </c>
+      <c r="I37" s="5">
+        <f>[1]data!$B$64</f>
+        <v>2.7</v>
+      </c>
+      <c r="J37" s="5">
+        <f t="shared" si="0"/>
+        <v>66.097117858865602</v>
+      </c>
       <c r="M37">
         <v>0.41907117300000002</v>
       </c>
@@ -21752,8 +20985,9 @@
       <c r="Q37">
         <v>2.304665542</v>
       </c>
-    </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T37" s="4"/>
+    </row>
+    <row r="38" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>57</v>
       </c>
@@ -21763,6 +20997,14 @@
       <c r="F38">
         <v>76.5</v>
       </c>
+      <c r="I38" s="5">
+        <f>[1]data!$B$64</f>
+        <v>2.7</v>
+      </c>
+      <c r="J38" s="5">
+        <f t="shared" si="0"/>
+        <v>66.179946327360398</v>
+      </c>
       <c r="M38">
         <v>-1.75917905</v>
       </c>
@@ -21772,8 +21014,9 @@
       <c r="Q38">
         <v>2.1654636310000002</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T38" s="4"/>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>58</v>
       </c>
@@ -21783,6 +21026,14 @@
       <c r="F39">
         <v>76.599999999999994</v>
       </c>
+      <c r="I39" s="5">
+        <f>[1]data!$B$64</f>
+        <v>2.7</v>
+      </c>
+      <c r="J39" s="5">
+        <f t="shared" si="0"/>
+        <v>66.511260201339695</v>
+      </c>
       <c r="M39">
         <v>-1.5814637730000001</v>
       </c>
@@ -21792,8 +21043,9 @@
       <c r="Q39">
         <v>2.1052631580000001</v>
       </c>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T39" s="4"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>59</v>
       </c>
@@ -21803,6 +21055,14 @@
       <c r="F40">
         <v>77.099999999999994</v>
       </c>
+      <c r="I40" s="5">
+        <f>[1]data!$B$64</f>
+        <v>2.7</v>
+      </c>
+      <c r="J40" s="5">
+        <f t="shared" si="0"/>
+        <v>66.925402543813789</v>
+      </c>
       <c r="M40">
         <v>-1.324149</v>
       </c>
@@ -21812,8 +21072,9 @@
       <c r="Q40">
         <v>2.2589531680000001</v>
       </c>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T40" s="4"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>60</v>
       </c>
@@ -21823,6 +21084,14 @@
       <c r="F41">
         <v>77.3</v>
       </c>
+      <c r="I41" s="5">
+        <f>[1]data!$B$65</f>
+        <v>2.9</v>
+      </c>
+      <c r="J41" s="5">
+        <f t="shared" si="0"/>
+        <v>68.071182140953255</v>
+      </c>
       <c r="M41">
         <v>-2.2268591369999999</v>
       </c>
@@ -21832,8 +21101,9 @@
       <c r="Q41">
         <v>2.1978021980000002</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T41" s="4"/>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>61</v>
       </c>
@@ -21843,6 +21113,14 @@
       <c r="F42">
         <v>78</v>
       </c>
+      <c r="I42" s="5">
+        <f>[1]data!$B$65</f>
+        <v>2.9</v>
+      </c>
+      <c r="J42" s="5">
+        <f t="shared" si="0"/>
+        <v>68.156484374212567</v>
+      </c>
       <c r="M42">
         <v>-47.585294716</v>
       </c>
@@ -21852,8 +21130,9 @@
       <c r="Q42">
         <v>2.2282608700000002</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T42" s="4"/>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>62</v>
       </c>
@@ -21863,6 +21142,14 @@
       <c r="F43">
         <v>78.400000000000006</v>
       </c>
+      <c r="I43" s="5">
+        <f>[1]data!$B$65</f>
+        <v>2.9</v>
+      </c>
+      <c r="J43" s="5">
+        <f t="shared" si="0"/>
+        <v>68.497693307249946</v>
+      </c>
       <c r="M43">
         <v>-15.433482809999999</v>
       </c>
@@ -21872,8 +21159,9 @@
       <c r="Q43">
         <v>2.3874118289999999</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T43" s="4"/>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>63</v>
       </c>
@@ -21883,6 +21171,14 @@
       <c r="F44">
         <v>78.8</v>
       </c>
+      <c r="I44" s="5">
+        <f>[1]data!$B$65</f>
+        <v>2.9</v>
+      </c>
+      <c r="J44" s="5">
+        <f t="shared" si="0"/>
+        <v>68.924204473546638</v>
+      </c>
       <c r="M44">
         <v>18.092172144999999</v>
       </c>
@@ -21892,8 +21188,9 @@
       <c r="Q44">
         <v>2.2629310340000002</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T44" s="4"/>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>64</v>
       </c>
@@ -21903,6 +21200,14 @@
       <c r="F45">
         <v>78.7</v>
       </c>
+      <c r="I45" s="5">
+        <f>[1]data!$B$66</f>
+        <v>3.1</v>
+      </c>
+      <c r="J45" s="5">
+        <f t="shared" si="0"/>
+        <v>70.248897978279928</v>
+      </c>
       <c r="M45">
         <v>53.577301192999997</v>
       </c>
@@ -21912,8 +21217,9 @@
       <c r="Q45">
         <v>2.2043010750000001</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T45" s="4"/>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>65</v>
       </c>
@@ -21923,6 +21229,14 @@
       <c r="F46">
         <v>79.8</v>
       </c>
+      <c r="I46" s="5">
+        <f>[1]data!$B$66</f>
+        <v>3.1</v>
+      </c>
+      <c r="J46" s="5">
+        <f t="shared" si="0"/>
+        <v>70.336929178753948</v>
+      </c>
       <c r="M46">
         <v>185.73924296300001</v>
       </c>
@@ -21932,8 +21246,9 @@
       <c r="Q46">
         <v>2.8176501859999998</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T46" s="4"/>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>66</v>
       </c>
@@ -21943,6 +21258,14 @@
       <c r="F47">
         <v>80.3</v>
       </c>
+      <c r="I47" s="5">
+        <f>[1]data!$B$66</f>
+        <v>3.1</v>
+      </c>
+      <c r="J47" s="5">
+        <f t="shared" si="0"/>
+        <v>70.689053980650101</v>
+      </c>
       <c r="M47">
         <v>33.836821596</v>
       </c>
@@ -21952,8 +21275,9 @@
       <c r="Q47">
         <v>3.2326444090000002</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T47" s="4"/>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>67</v>
       </c>
@@ -21963,6 +21287,14 @@
       <c r="F48">
         <v>80.900000000000006</v>
       </c>
+      <c r="I48" s="5">
+        <f>[1]data!$B$66</f>
+        <v>3.1</v>
+      </c>
+      <c r="J48" s="5">
+        <f t="shared" si="0"/>
+        <v>71.129209983020274</v>
+      </c>
       <c r="M48">
         <v>-22.755315791000001</v>
       </c>
@@ -21972,8 +21304,9 @@
       <c r="Q48">
         <v>3.4773445729999999</v>
       </c>
-    </row>
-    <row r="49" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T48" s="4"/>
+    </row>
+    <row r="49" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>68</v>
       </c>
@@ -21983,6 +21316,14 @@
       <c r="F49">
         <v>81</v>
       </c>
+      <c r="I49" s="5">
+        <f>[1]data!$B$67</f>
+        <v>2</v>
+      </c>
+      <c r="J49" s="5">
+        <f t="shared" si="0"/>
+        <v>71.682548957428494</v>
+      </c>
       <c r="M49">
         <v>-24.393466524000001</v>
       </c>
@@ -21992,8 +21333,9 @@
       <c r="Q49">
         <v>3.7348763809999999</v>
       </c>
-    </row>
-    <row r="50" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T49" s="4"/>
+    </row>
+    <row r="50" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>69</v>
       </c>
@@ -22003,6 +21345,14 @@
       <c r="F50">
         <v>81.8</v>
       </c>
+      <c r="I50" s="5">
+        <f>[1]data!$B$67</f>
+        <v>2</v>
+      </c>
+      <c r="J50" s="5">
+        <f t="shared" si="0"/>
+        <v>71.772376713014239</v>
+      </c>
       <c r="M50">
         <v>-28.156065305999999</v>
       </c>
@@ -22012,8 +21362,9 @@
       <c r="Q50">
         <v>3.4126163389999999</v>
       </c>
-    </row>
-    <row r="51" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T50" s="4"/>
+    </row>
+    <row r="51" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>70</v>
       </c>
@@ -22023,6 +21374,14 @@
       <c r="F51">
         <v>81.7</v>
       </c>
+      <c r="I51" s="5">
+        <f>[1]data!$B$67</f>
+        <v>2</v>
+      </c>
+      <c r="J51" s="5">
+        <f t="shared" si="0"/>
+        <v>72.131687735357247</v>
+      </c>
       <c r="M51">
         <v>-7.5549285629999998</v>
       </c>
@@ -22032,8 +21391,9 @@
       <c r="Q51">
         <v>2.72073922</v>
       </c>
-    </row>
-    <row r="52" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T51" s="4"/>
+    </row>
+    <row r="52" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>71</v>
       </c>
@@ -22043,6 +21403,14 @@
       <c r="F52">
         <v>82.6</v>
       </c>
+      <c r="I52" s="5">
+        <f>[1]data!$B$67</f>
+        <v>2</v>
+      </c>
+      <c r="J52" s="5">
+        <f t="shared" si="0"/>
+        <v>72.580826513285999</v>
+      </c>
       <c r="M52">
         <v>14.350458784000001</v>
       </c>
@@ -22052,8 +21420,9 @@
       <c r="Q52">
         <v>3.1059063139999998</v>
       </c>
-    </row>
-    <row r="53" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T52" s="4"/>
+    </row>
+    <row r="53" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>72</v>
       </c>
@@ -22063,6 +21432,14 @@
       <c r="F53">
         <v>82.924333333000007</v>
       </c>
+      <c r="I53" s="5">
+        <f>[1]data!$B$68</f>
+        <v>3.3</v>
+      </c>
+      <c r="J53" s="5">
+        <f t="shared" si="0"/>
+        <v>74.128799335499991</v>
+      </c>
       <c r="M53">
         <v>-16.975503931999999</v>
       </c>
@@ -22072,8 +21449,9 @@
       <c r="Q53">
         <v>3.4989858009999999</v>
       </c>
-    </row>
-    <row r="54" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T53" s="4"/>
+    </row>
+    <row r="54" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>73</v>
       </c>
@@ -22083,6 +21461,14 @@
       <c r="F54">
         <v>84.597333332999995</v>
       </c>
+      <c r="I54" s="5">
+        <f>[1]data!$B$68</f>
+        <v>3.3</v>
+      </c>
+      <c r="J54" s="5">
+        <f t="shared" si="0"/>
+        <v>74.221692567749997</v>
+      </c>
       <c r="M54">
         <v>-22.750338828</v>
       </c>
@@ -22092,8 +21478,9 @@
       <c r="Q54">
         <v>4.3833333330000004</v>
       </c>
-    </row>
-    <row r="55" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T54" s="4"/>
+    </row>
+    <row r="55" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>74</v>
       </c>
@@ -22103,6 +21490,14 @@
       <c r="F55">
         <v>85.653333333000006</v>
       </c>
+      <c r="I55" s="5">
+        <f>[1]data!$B$68</f>
+        <v>3.3</v>
+      </c>
+      <c r="J55" s="5">
+        <f t="shared" si="0"/>
+        <v>74.593265496749993</v>
+      </c>
       <c r="M55">
         <v>-16.698594109999998</v>
       </c>
@@ -22112,8 +21507,9 @@
       <c r="Q55">
         <v>5.3473263370000002</v>
       </c>
-    </row>
-    <row r="56" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T55" s="4"/>
+    </row>
+    <row r="56" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>75</v>
       </c>
@@ -22123,6 +21519,14 @@
       <c r="F56">
         <v>85.758666667</v>
       </c>
+      <c r="I56" s="5">
+        <f>[1]data!$B$68</f>
+        <v>3.3</v>
+      </c>
+      <c r="J56" s="5">
+        <f t="shared" si="0"/>
+        <v>75.057731657999994</v>
+      </c>
       <c r="M56">
         <v>-20.037684361</v>
       </c>
@@ -22132,8 +21536,9 @@
       <c r="Q56">
         <v>3.7860082300000002</v>
       </c>
-    </row>
-    <row r="57" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T56" s="4"/>
+    </row>
+    <row r="57" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
         <v>76</v>
       </c>
@@ -22143,6 +21548,14 @@
       <c r="F57">
         <v>85.416666667000001</v>
       </c>
+      <c r="I57" s="5">
+        <f>[1]data!$B$69</f>
+        <v>2</v>
+      </c>
+      <c r="J57" s="5">
+        <f t="shared" si="0"/>
+        <v>75.641631974999996</v>
+      </c>
       <c r="M57">
         <v>-7.987661042</v>
       </c>
@@ -22152,8 +21565,9 @@
       <c r="Q57">
         <v>2.3844520660000001</v>
       </c>
-    </row>
-    <row r="58" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T57" s="4"/>
+    </row>
+    <row r="58" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>77</v>
       </c>
@@ -22163,6 +21577,14 @@
       <c r="F58">
         <v>86.364333333000005</v>
       </c>
+      <c r="I58" s="5">
+        <f>[1]data!$B$69</f>
+        <v>2</v>
+      </c>
+      <c r="J58" s="5">
+        <f t="shared" si="0"/>
+        <v>75.736420987499997</v>
+      </c>
       <c r="M58">
         <v>11.587580073</v>
       </c>
@@ -22172,8 +21594,9 @@
       <c r="Q58">
         <v>1.4370110169999999</v>
       </c>
-    </row>
-    <row r="59" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T58" s="4"/>
+    </row>
+    <row r="59" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>78</v>
       </c>
@@ -22183,6 +21606,14 @@
       <c r="F59">
         <v>86.929333333000002</v>
       </c>
+      <c r="I59" s="5">
+        <f>[1]data!$B$69</f>
+        <v>2</v>
+      </c>
+      <c r="J59" s="5">
+        <f t="shared" si="0"/>
+        <v>76.115577037499989</v>
+      </c>
       <c r="M59">
         <v>7.397879638</v>
       </c>
@@ -22192,8 +21623,9 @@
       <c r="Q59">
         <v>1.312460468</v>
       </c>
-    </row>
-    <row r="60" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T59" s="4"/>
+    </row>
+    <row r="60" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>79</v>
       </c>
@@ -22203,6 +21635,14 @@
       <c r="F60">
         <v>87.562333332999998</v>
       </c>
+      <c r="I60" s="5">
+        <f>[1]data!$B$69</f>
+        <v>2</v>
+      </c>
+      <c r="J60" s="5">
+        <f t="shared" si="0"/>
+        <v>76.589522099999996</v>
+      </c>
       <c r="L60">
         <v>290.83999999999997</v>
       </c>
@@ -22215,8 +21655,9 @@
       <c r="Q60">
         <v>2.7914353690000002</v>
       </c>
-    </row>
-    <row r="61" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T60" s="4"/>
+    </row>
+    <row r="61" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>80</v>
       </c>
@@ -22226,6 +21667,14 @@
       <c r="F61">
         <v>88.213666666999998</v>
       </c>
+      <c r="I61" s="5">
+        <f>[1]data!$B$70</f>
+        <v>1.3</v>
+      </c>
+      <c r="J61" s="5">
+        <f t="shared" si="0"/>
+        <v>76.637924999999996</v>
+      </c>
       <c r="L61">
         <v>310.977755</v>
       </c>
@@ -22238,8 +21687,9 @@
       <c r="Q61">
         <v>4.5461796139999997</v>
       </c>
-    </row>
-    <row r="62" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T61" s="4"/>
+    </row>
+    <row r="62" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>81</v>
       </c>
@@ -22249,6 +21699,14 @@
       <c r="F62">
         <v>89.349666666999994</v>
       </c>
+      <c r="I62" s="5">
+        <f>[1]data!$B$70</f>
+        <v>1.3</v>
+      </c>
+      <c r="J62" s="5">
+        <f t="shared" ref="J62:J67" si="1">J66*(1-I66/100)</f>
+        <v>76.733962500000004</v>
+      </c>
       <c r="L62">
         <v>263.107056</v>
       </c>
@@ -22261,8 +21719,9 @@
       <c r="Q62">
         <v>5.1629151579999997</v>
       </c>
-    </row>
-    <row r="63" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T62" s="4"/>
+    </row>
+    <row r="63" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
         <v>82</v>
       </c>
@@ -22272,6 +21731,14 @@
       <c r="F63">
         <v>89.611333333000005</v>
       </c>
+      <c r="I63" s="5">
+        <f>[1]data!$B$70</f>
+        <v>1.3</v>
+      </c>
+      <c r="J63" s="5">
+        <f t="shared" si="1"/>
+        <v>77.118112499999995</v>
+      </c>
       <c r="L63">
         <v>279.28384599999998</v>
       </c>
@@ -22284,8 +21751,9 @@
       <c r="Q63">
         <v>4.6823786480000003</v>
       </c>
-    </row>
-    <row r="64" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T63" s="4"/>
+    </row>
+    <row r="64" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>83</v>
       </c>
@@ -22295,6 +21763,14 @@
       <c r="F64">
         <v>90.518666667000005</v>
       </c>
+      <c r="I64" s="5">
+        <f>[1]data!$B$70</f>
+        <v>1.3</v>
+      </c>
+      <c r="J64" s="5">
+        <f t="shared" si="1"/>
+        <v>77.598299999999995</v>
+      </c>
       <c r="L64">
         <v>296.90782999999999</v>
       </c>
@@ -22307,8 +21783,9 @@
       <c r="Q64">
         <v>4.6597747260000002</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T64" s="4"/>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>84</v>
       </c>
@@ -22318,6 +21795,14 @@
       <c r="F65">
         <v>91.846666666999994</v>
       </c>
+      <c r="I65" s="5">
+        <f>[1]data!$B$71</f>
+        <v>2.5</v>
+      </c>
+      <c r="J65" s="5">
+        <f t="shared" si="1"/>
+        <v>78.602999999999994</v>
+      </c>
       <c r="L65">
         <v>302.59850699999998</v>
       </c>
@@ -22330,8 +21815,9 @@
       <c r="Q65">
         <v>5.3402502289999996</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T65" s="4"/>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>85</v>
       </c>
@@ -22341,6 +21827,14 @@
       <c r="F66">
         <v>93.260666666999995</v>
       </c>
+      <c r="I66" s="5">
+        <f>[1]data!$B$71</f>
+        <v>2.5</v>
+      </c>
+      <c r="J66" s="5">
+        <f t="shared" si="1"/>
+        <v>78.70150000000001</v>
+      </c>
       <c r="L66">
         <v>306.34029099999998</v>
       </c>
@@ -22353,8 +21847,9 @@
       <c r="Q66">
         <v>5.178865439</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T66" s="4"/>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>86</v>
       </c>
@@ -22364,6 +21859,14 @@
       <c r="F67">
         <v>93.828333333000003</v>
       </c>
+      <c r="I67" s="5">
+        <f>[1]data!$B$71</f>
+        <v>2.5</v>
+      </c>
+      <c r="J67" s="5">
+        <f t="shared" si="1"/>
+        <v>79.095500000000001</v>
+      </c>
       <c r="L67">
         <v>311.12984799999998</v>
       </c>
@@ -22376,8 +21879,9 @@
       <c r="Q67">
         <v>5.3526166689999997</v>
       </c>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T67" s="4"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>87</v>
       </c>
@@ -22387,6 +21891,14 @@
       <c r="F68">
         <v>94.724000000000004</v>
       </c>
+      <c r="I68" s="5">
+        <f>[1]data!$B$71</f>
+        <v>2.5</v>
+      </c>
+      <c r="J68" s="5">
+        <f>J72*(1-I72/100)</f>
+        <v>79.587999999999994</v>
+      </c>
       <c r="L68">
         <v>316.85687899999999</v>
       </c>
@@ -22399,8 +21911,9 @@
       <c r="Q68">
         <v>5.2779006339999999</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T68" s="4"/>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>88</v>
       </c>
@@ -22410,6 +21923,10 @@
       <c r="F69">
         <v>95.052333333000007</v>
       </c>
+      <c r="I69" s="5">
+        <f>[1]data!$B$72</f>
+        <v>1.5</v>
+      </c>
       <c r="J69">
         <v>79.8</v>
       </c>
@@ -22425,8 +21942,9 @@
       <c r="Q69">
         <v>3.8238702199999999</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T69" s="4"/>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>89</v>
       </c>
@@ -22436,6 +21954,10 @@
       <c r="F70">
         <v>95.830333332999999</v>
       </c>
+      <c r="I70" s="5">
+        <f>[1]data!$B$72</f>
+        <v>1.5</v>
+      </c>
       <c r="J70">
         <v>79.900000000000006</v>
       </c>
@@ -22451,8 +21973,9 @@
       <c r="Q70">
         <v>3.1450120959999999</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T70" s="4"/>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
         <v>90</v>
       </c>
@@ -22462,6 +21985,10 @@
       <c r="F71">
         <v>96.091999999999999</v>
       </c>
+      <c r="I71" s="5">
+        <f>[1]data!$B$72</f>
+        <v>1.5</v>
+      </c>
       <c r="J71">
         <v>80.3</v>
       </c>
@@ -22477,8 +22004,9 @@
       <c r="Q71">
         <v>2.9012170959999999</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T71" s="4"/>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>91</v>
       </c>
@@ -22488,6 +22016,10 @@
       <c r="F72">
         <v>97.253</v>
       </c>
+      <c r="I72" s="5">
+        <f>[1]data!$B$72</f>
+        <v>1.5</v>
+      </c>
       <c r="J72">
         <v>80.8</v>
       </c>
@@ -22503,8 +22035,9 @@
       <c r="Q72">
         <v>3.0107828040000002</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T72" s="4"/>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
         <v>92</v>
       </c>
@@ -22532,8 +22065,9 @@
       <c r="Q73">
         <v>3.2366071430000001</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T73" s="4"/>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>93</v>
       </c>
@@ -22561,8 +22095,9 @@
       <c r="Q74">
         <v>3.062913907</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T74" s="4"/>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>94</v>
       </c>
@@ -22590,8 +22125,9 @@
       <c r="Q75">
         <v>3.218264338</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T75" s="4"/>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>95</v>
       </c>
@@ -22619,8 +22155,9 @@
       <c r="Q76">
         <v>2.7052746060000001</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T76" s="4"/>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>96</v>
       </c>
@@ -22648,8 +22185,9 @@
       <c r="Q77">
         <v>2.675675676</v>
       </c>
-    </row>
-    <row r="78" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T77" s="4"/>
+    </row>
+    <row r="78" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>97</v>
       </c>
@@ -22677,8 +22215,9 @@
       <c r="Q78">
         <v>2.597054886</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T78" s="4"/>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>98</v>
       </c>
@@ -22706,8 +22245,9 @@
       <c r="Q79">
         <v>2.4783477679999999</v>
       </c>
-    </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T79" s="4"/>
+    </row>
+    <row r="80" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>99</v>
       </c>
@@ -22735,8 +22275,9 @@
       <c r="Q80">
         <v>2.0251489079999998</v>
       </c>
-    </row>
-    <row r="81" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T80" s="4"/>
+    </row>
+    <row r="81" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>100</v>
       </c>
@@ -22764,8 +22305,9 @@
       <c r="Q81">
         <v>1.026585944</v>
       </c>
-    </row>
-    <row r="82" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T81" s="4"/>
+    </row>
+    <row r="82" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>101</v>
       </c>
@@ -22790,8 +22332,9 @@
       <c r="Q82">
         <v>1.0046972860000001</v>
       </c>
-    </row>
-    <row r="83" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T82" s="4"/>
+    </row>
+    <row r="83" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>102</v>
       </c>
@@ -22816,8 +22359,9 @@
       <c r="Q83">
         <v>1.02717462</v>
       </c>
-    </row>
-    <row r="84" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T83" s="4"/>
+    </row>
+    <row r="84" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>103</v>
       </c>
@@ -22842,8 +22386,9 @@
       <c r="Q84">
         <v>1.0508562530000001</v>
       </c>
-    </row>
-    <row r="85" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T84" s="4"/>
+    </row>
+    <row r="85" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>104</v>
       </c>
@@ -22868,8 +22413,9 @@
       <c r="Q85">
         <v>1.4721208960000001</v>
       </c>
-    </row>
-    <row r="86" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T85" s="4"/>
+    </row>
+    <row r="86" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>105</v>
       </c>
@@ -22894,8 +22440,9 @@
       <c r="Q86">
         <v>1.5243508589999999</v>
       </c>
-    </row>
-    <row r="87" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T86" s="4"/>
+    </row>
+    <row r="87" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>106</v>
       </c>
@@ -22920,8 +22467,9 @@
       <c r="Q87">
         <v>2.007722008</v>
       </c>
-    </row>
-    <row r="88" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T87" s="4"/>
+    </row>
+    <row r="88" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>107</v>
       </c>
@@ -22946,8 +22494,9 @@
       <c r="Q88">
         <v>2.4778533829999998</v>
       </c>
-    </row>
-    <row r="89" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T88" s="4"/>
+    </row>
+    <row r="89" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>108</v>
       </c>
@@ -22972,8 +22521,9 @@
       <c r="Q89">
         <v>3.2610091149999998</v>
       </c>
-    </row>
-    <row r="90" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T89" s="4"/>
+    </row>
+    <row r="90" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B90" t="s">
         <v>109</v>
       </c>
@@ -22998,8 +22548,9 @@
       <c r="Q90">
         <v>3.8300038170000001</v>
       </c>
-    </row>
-    <row r="91" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T90" s="4"/>
+    </row>
+    <row r="91" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B91" t="s">
         <v>110</v>
       </c>
@@ -23024,8 +22575,9 @@
       <c r="Q91">
         <v>4.0247287409999997</v>
       </c>
-    </row>
-    <row r="92" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T91" s="4"/>
+    </row>
+    <row r="92" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B92" t="s">
         <v>111</v>
       </c>
@@ -23050,8 +22602,9 @@
       <c r="Q92">
         <v>4.0967176150000002</v>
       </c>
-    </row>
-    <row r="93" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T92" s="4"/>
+    </row>
+    <row r="93" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B93" t="s">
         <v>112</v>
       </c>
@@ -23076,8 +22629,9 @@
       <c r="Q93">
         <v>3.6802188240000002</v>
       </c>
-    </row>
-    <row r="94" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T93" s="4"/>
+    </row>
+    <row r="94" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
         <v>113</v>
       </c>
@@ -23102,8 +22656,9 @@
       <c r="Q94">
         <v>3.3823529410000002</v>
       </c>
-    </row>
-    <row r="95" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T94" s="4"/>
+    </row>
+    <row r="95" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B95" t="s">
         <v>114</v>
       </c>
@@ -23128,8 +22683,9 @@
       <c r="Q95">
         <v>3.2989690719999998</v>
       </c>
-    </row>
-    <row r="96" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T95" s="4"/>
+    </row>
+    <row r="96" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
         <v>115</v>
       </c>
@@ -23154,8 +22710,9 @@
       <c r="Q96">
         <v>3.008785654</v>
       </c>
-    </row>
-    <row r="97" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T96" s="4"/>
+    </row>
+    <row r="97" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
         <v>116</v>
       </c>
@@ -23180,8 +22737,9 @@
       <c r="Q97">
         <v>2.4463364909999998</v>
       </c>
-    </row>
-    <row r="98" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T97" s="4"/>
+    </row>
+    <row r="98" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>117</v>
       </c>
@@ -23206,8 +22764,9 @@
       <c r="Q98">
         <v>2.9397818870000001</v>
       </c>
-    </row>
-    <row r="99" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T98" s="4"/>
+    </row>
+    <row r="99" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>118</v>
       </c>
@@ -23232,8 +22791,9 @@
       <c r="Q99">
         <v>2.5830691560000001</v>
       </c>
-    </row>
-    <row r="100" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T99" s="4"/>
+    </row>
+    <row r="100" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
         <v>119</v>
       </c>
@@ -23258,8 +22818,9 @@
       <c r="Q100">
         <v>2.2198855009999998</v>
       </c>
-    </row>
-    <row r="101" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T100" s="4"/>
+    </row>
+    <row r="101" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
         <v>120</v>
       </c>
@@ -23284,8 +22845,9 @@
       <c r="Q101">
         <v>2.668851691</v>
       </c>
-    </row>
-    <row r="102" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T101" s="4"/>
+    </row>
+    <row r="102" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
         <v>121</v>
       </c>
@@ -23310,8 +22872,9 @@
       <c r="Q102">
         <v>1.3818516810000001</v>
       </c>
-    </row>
-    <row r="103" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T102" s="4"/>
+    </row>
+    <row r="103" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>122</v>
       </c>
@@ -23336,8 +22899,9 @@
       <c r="Q103">
         <v>1.3391324250000001</v>
       </c>
-    </row>
-    <row r="104" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T103" s="4"/>
+    </row>
+    <row r="104" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>123</v>
       </c>
@@ -23362,8 +22926,9 @@
       <c r="Q104">
         <v>1.360155446</v>
       </c>
-    </row>
-    <row r="105" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T104" s="4"/>
+    </row>
+    <row r="105" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
         <v>124</v>
       </c>
@@ -23388,8 +22953,9 @@
       <c r="Q105">
         <v>1.596169194</v>
       </c>
-    </row>
-    <row r="106" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T105" s="4"/>
+    </row>
+    <row r="106" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>125</v>
       </c>
@@ -23414,8 +22980,9 @@
       <c r="Q106">
         <v>3.509768287</v>
       </c>
-    </row>
-    <row r="107" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T106" s="4"/>
+    </row>
+    <row r="107" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
         <v>126</v>
       </c>
@@ -23440,8 +23007,9 @@
       <c r="Q107">
         <v>4.5967924099999999</v>
       </c>
-    </row>
-    <row r="108" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T107" s="4"/>
+    </row>
+    <row r="108" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
         <v>127</v>
       </c>
@@ -23466,8 +23034,9 @@
       <c r="Q108">
         <v>7.0252593589999996</v>
       </c>
-    </row>
-    <row r="109" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T108" s="4"/>
+    </row>
+    <row r="109" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
         <v>128</v>
       </c>
@@ -23492,8 +23061,9 @@
       <c r="Q109">
         <v>8.4838963080000003</v>
       </c>
-    </row>
-    <row r="110" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T109" s="4"/>
+    </row>
+    <row r="110" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
         <v>129</v>
       </c>
@@ -23518,8 +23088,9 @@
       <c r="Q110">
         <v>11.631734884</v>
       </c>
-    </row>
-    <row r="111" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T110" s="4"/>
+    </row>
+    <row r="111" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
         <v>130</v>
       </c>
@@ -23544,8 +23115,9 @@
       <c r="Q111">
         <v>12.320483748999999</v>
       </c>
-    </row>
-    <row r="112" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T111" s="4"/>
+    </row>
+    <row r="112" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
         <v>131</v>
       </c>
@@ -23570,8 +23142,9 @@
       <c r="Q112">
         <v>13.423243072</v>
       </c>
-    </row>
-    <row r="113" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T112" s="4"/>
+    </row>
+    <row r="113" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
         <v>132</v>
       </c>
@@ -23596,8 +23169,9 @@
       <c r="Q113">
         <v>12.703010240999999</v>
       </c>
-    </row>
-    <row r="114" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T113" s="4"/>
+    </row>
+    <row r="114" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
         <v>133</v>
       </c>
@@ -23622,8 +23196,9 @@
       <c r="Q114">
         <v>10.085520495000001</v>
       </c>
-    </row>
-    <row r="115" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T114" s="4"/>
+    </row>
+    <row r="115" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
         <v>134</v>
       </c>
@@ -23648,8 +23223,9 @@
       <c r="Q115">
         <v>7.7581234380000001</v>
       </c>
-    </row>
-    <row r="116" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T115" s="4"/>
+    </row>
+    <row r="116" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
         <v>135</v>
       </c>
@@ -23674,8 +23250,9 @@
       <c r="Q116">
         <v>4.3009753829999999</v>
       </c>
-    </row>
-    <row r="117" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T116" s="4"/>
+    </row>
+    <row r="117" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
         <v>136</v>
       </c>
@@ -23700,8 +23277,9 @@
       <c r="Q117">
         <v>3.542909592</v>
       </c>
-    </row>
-    <row r="118" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T117" s="4"/>
+    </row>
+    <row r="118" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
         <v>137</v>
       </c>
@@ -23726,8 +23304,9 @@
       <c r="Q118">
         <v>2.0716135370000002</v>
       </c>
-    </row>
-    <row r="119" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T118" s="4"/>
+    </row>
+    <row r="119" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
         <v>138</v>
       </c>
@@ -23752,8 +23331,9 @@
       <c r="Q119">
         <v>2.5158354890000001</v>
       </c>
-    </row>
-    <row r="120" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T119" s="4"/>
+    </row>
+    <row r="120" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
         <v>4</v>
       </c>
@@ -23802,8 +23382,9 @@
       <c r="Q120">
         <v>2.921268258</v>
       </c>
-    </row>
-    <row r="121" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T120" s="4"/>
+    </row>
+    <row r="121" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
         <v>5</v>
       </c>
@@ -23831,8 +23412,9 @@
       <c r="P121">
         <v>387.25020143</v>
       </c>
-    </row>
-    <row r="122" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T121" s="4"/>
+    </row>
+    <row r="122" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
         <v>6</v>
       </c>
@@ -23860,8 +23442,9 @@
       <c r="P122">
         <v>395.38007170899999</v>
       </c>
-    </row>
-    <row r="123" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T122" s="4"/>
+    </row>
+    <row r="123" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>7</v>
       </c>
@@ -23889,8 +23472,9 @@
       <c r="P123">
         <v>399.24234003999999</v>
       </c>
-    </row>
-    <row r="124" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T123" s="4"/>
+    </row>
+    <row r="124" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
         <v>8</v>
       </c>
@@ -23918,8 +23502,9 @@
       <c r="P124">
         <v>400.00910879499997</v>
       </c>
-    </row>
-    <row r="125" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T124" s="4"/>
+    </row>
+    <row r="125" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>9</v>
       </c>
@@ -23947,8 +23532,9 @@
       <c r="P125">
         <v>400.16546693700002</v>
       </c>
-    </row>
-    <row r="126" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T125" s="4"/>
+    </row>
+    <row r="126" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
         <v>10</v>
       </c>
@@ -23976,8 +23562,9 @@
       <c r="P126">
         <v>406.35739039100002</v>
       </c>
-    </row>
-    <row r="127" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T126" s="4"/>
+    </row>
+    <row r="127" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
         <v>11</v>
       </c>
@@ -24005,8 +23592,9 @@
       <c r="P127">
         <v>409.48403756800002</v>
       </c>
-    </row>
-    <row r="128" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T127" s="4"/>
+    </row>
+    <row r="128" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
         <v>12</v>
       </c>
@@ -24034,8 +23622,9 @@
       <c r="P128">
         <v>410.645207212</v>
       </c>
-    </row>
-    <row r="129" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T128" s="4"/>
+    </row>
+    <row r="129" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
         <v>13</v>
       </c>
@@ -24063,8 +23652,9 @@
       <c r="P129">
         <v>411.115501107</v>
       </c>
-    </row>
-    <row r="130" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T129" s="4"/>
+    </row>
+    <row r="130" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
         <v>14</v>
       </c>
@@ -24092,8 +23682,9 @@
       <c r="P130">
         <v>417.53208657699997</v>
       </c>
-    </row>
-    <row r="131" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T130" s="4"/>
+    </row>
+    <row r="131" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
         <v>15</v>
       </c>
@@ -24121,8 +23712,9 @@
       <c r="P131">
         <v>420.81526642799997</v>
       </c>
-    </row>
-    <row r="132" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T131" s="4"/>
+    </row>
+    <row r="132" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
         <v>16</v>
       </c>
@@ -24150,8 +23742,9 @@
       <c r="P132">
         <v>422.00201087699998</v>
       </c>
-    </row>
-    <row r="133" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T132" s="4"/>
+    </row>
+    <row r="133" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
         <v>17</v>
       </c>
@@ -24179,8 +23772,9 @@
       <c r="P133">
         <v>422.48366991799998</v>
       </c>
-    </row>
-    <row r="134" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T133" s="4"/>
+    </row>
+    <row r="134" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
         <v>18</v>
       </c>
@@ -24208,8 +23802,9 @@
       <c r="P134">
         <v>429.06611737499998</v>
       </c>
-    </row>
-    <row r="135" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T134" s="4"/>
+    </row>
+    <row r="135" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
         <v>19</v>
       </c>
@@ -24237,8 +23832,9 @@
       <c r="P135">
         <v>432.42554649499999</v>
       </c>
-    </row>
-    <row r="136" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T135" s="4"/>
+    </row>
+    <row r="136" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
         <v>20</v>
       </c>
@@ -24266,8 +23862,9 @@
       <c r="P136">
         <v>433.63544005400001</v>
       </c>
-    </row>
-    <row r="137" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T136" s="4"/>
+    </row>
+    <row r="137" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
         <v>21</v>
       </c>
@@ -24295,8 +23892,9 @@
       <c r="P137">
         <v>434.12468310499997</v>
       </c>
-    </row>
-    <row r="138" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T137" s="4"/>
+    </row>
+    <row r="138" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
         <v>22</v>
       </c>
@@ -24324,8 +23922,9 @@
       <c r="P138">
         <v>440.89192277900003</v>
       </c>
-    </row>
-    <row r="139" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T138" s="4"/>
+    </row>
+    <row r="139" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
         <v>23</v>
       </c>
@@ -24353,8 +23952,9 @@
       <c r="P139">
         <v>444.34796822999999</v>
       </c>
-    </row>
-    <row r="140" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T139" s="4"/>
+    </row>
+    <row r="140" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
         <v>24</v>
       </c>
@@ -24382,8 +23982,9 @@
       <c r="P140">
         <v>445.58618410600002</v>
       </c>
-    </row>
-    <row r="141" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T140" s="4"/>
+    </row>
+    <row r="141" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
         <v>25</v>
       </c>
@@ -24411,8 +24012,9 @@
       <c r="P141">
         <v>445.77710016700001</v>
       </c>
-    </row>
-    <row r="142" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="T141" s="4"/>
+    </row>
+    <row r="142" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
         <v>156</v>
       </c>
